--- a/assets/downloads/world500_unmatched_diagnosis.xlsx
+++ b/assets/downloads/world500_unmatched_diagnosis.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'分类汇总'!$A$3:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'174条诊断总表'!$A$3:$M$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'174条诊断总表'!$A$3:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +557,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>174 条未匹配诊断表</t>
+          <t>167 条未匹配诊断表</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -589,7 +589,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>本表仅针对 world500_match_review.csv 中当前 review_decision 为空的 174 条未决匹配进行诊断。</t>
+          <t>本表仅针对 world500_match_review.csv 中当前 review_decision 为空的 167 条未决匹配进行诊断。</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -645,7 +645,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>未决匹配总数：171</t>
+          <t>未决匹配总数：167</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>库存文件总数：387</t>
+          <t>库存文件总数：396</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -669,7 +669,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>生成时间：2026-04-12 22:09:28</t>
+          <t>生成时间：2026-04-15 18:50:53</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -722,7 +722,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>本页汇总 174 条未决匹配在四种诊断类别下的数量分布。</t>
+          <t>本页汇总 167 条未决匹配在四种诊断类别下的数量分布。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1632,22 +1632,22 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>r114_royalaholddelhaize</t>
+          <t>r118_créditagricole</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>皇家阿霍德德尔海兹集团</t>
+          <t>法国农业信贷银行</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>ROYAL AHOLD DELHAIZE</t>
+          <t>CRÉDIT AGRICOLE</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1665,12 +1665,12 @@
       <c r="I15" s="9" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“皇家阿霍德德尔海兹集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国农业信贷银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ROYAL AHOLD DELHAIZE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT AGRICOLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -1687,22 +1687,22 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>r118_créditagricole</t>
+          <t>r119_christiandior</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>法国农业信贷银行</t>
+          <t>迪奥公司</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>CRÉDIT AGRICOLE</t>
+          <t>CHRISTIAN DIOR</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1720,12 +1720,12 @@
       <c r="I16" s="9" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国农业信贷银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“迪奥公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT AGRICOLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHRISTIAN DIOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -1742,22 +1742,22 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>r119_christiandior</t>
+          <t>r122_carrefour</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>迪奥公司</t>
+          <t>家乐福</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>CHRISTIAN DIOR</t>
+          <t>CARREFOUR</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1775,12 +1775,12 @@
       <c r="I17" s="9" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“迪奥公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“家乐福”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHRISTIAN DIOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CARREFOUR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -1797,22 +1797,22 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>r122_carrefour</t>
+          <t>r129_chinafawgroup</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>家乐福</t>
+          <t>中国第一汽车集团有限公司</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>CARREFOUR</t>
+          <t>CHINA FAW GROUP</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1830,12 +1830,12 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“家乐福”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国第一汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CARREFOUR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA FAW GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -1852,22 +1852,22 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>r129_chinafawgroup</t>
+          <t>r138_zhejiangrongshengholdinggroup</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>中国第一汽车集团有限公司</t>
+          <t>浙江荣盛控股集团有限公司</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>CHINA FAW GROUP</t>
+          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1885,12 +1885,12 @@
       <c r="I19" s="9" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国第一汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA FAW GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG RONGSHENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -1907,22 +1907,22 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>r138_zhejiangrongshengholdinggroup</t>
+          <t>r142_xiamenitgholdinggroup</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>浙江荣盛控股集团有限公司</t>
+          <t>厦门国贸控股集团有限公司</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
+          <t>XIAMEN ITG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1940,12 +1940,12 @@
       <c r="I20" s="9" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG RONGSHENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'XIAMEN ITG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -1962,22 +1962,22 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>r142_xiamenitgholdinggroup</t>
+          <t>r147_aviationindustrycorpofchina</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>厦门国贸控股集团有限公司</t>
+          <t>中国航空工业集团有限公司</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>XIAMEN ITG HOLDING GROUP</t>
+          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1995,12 +1995,12 @@
       <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'XIAMEN ITG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AVIATION INDUSTRY CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -2017,22 +2017,22 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>r147_aviationindustrycorpofchina</t>
+          <t>r155_energytransfer公司</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>中国航空工业集团有限公司</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2050,12 +2050,12 @@
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AVIATION INDUSTRY CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Energy Transfer公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2072,22 +2072,22 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>r155_energytransfer公司</t>
+          <t>r160_chinanorthindustriesgroup</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>中国兵器工业集团有限公司</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>CHINA NORTH INDUSTRIES GROUP</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2105,12 +2105,12 @@
       <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Energy Transfer公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NORTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -2127,22 +2127,22 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>r156_uspostalservice</t>
+          <t>r161_pacificconstructiongroup</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>美国邮政</t>
+          <t>太平洋建设集团有限公司</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>U.S. POSTAL SERVICE</t>
+          <t>PACIFIC CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2160,12 +2160,12 @@
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国邮政”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'U.S. POSTAL SERVICE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PACIFIC CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -2182,22 +2182,22 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>r160_chinanorthindustriesgroup</t>
+          <t>r167_petronas</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司</t>
+          <t>马来西亚国家石油公司</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>CHINA NORTH INDUSTRIES GROUP</t>
+          <t>PETRONAS</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2215,12 +2215,12 @@
       <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“马来西亚国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NORTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PETRONAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -2237,22 +2237,22 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>r161_pacificconstructiongroup</t>
+          <t>r171_shenghongholdinggroup</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>太平洋建设集团有限公司</t>
+          <t>盛虹控股集团有限公司</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>PACIFIC CONSTRUCTION GROUP</t>
+          <t>SHENGHONG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2270,12 +2270,12 @@
       <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“盛虹控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PACIFIC CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHENGHONG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -2292,22 +2292,22 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>r167_petronas</t>
+          <t>r172_basf</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>172</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>马来西亚国家石油公司</t>
+          <t>巴斯夫公司</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>PETRONAS</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2325,12 +2325,12 @@
       <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“马来西亚国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴斯夫公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PETRONAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BASF'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -2347,22 +2347,22 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>r171_shenghongholdinggroup</t>
+          <t>r175_shandongweiqiaopioneeringgroup</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>盛虹控股集团有限公司</t>
+          <t>山东魏桥创业集团有限公司</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>SHENGHONG HOLDING GROUP</t>
+          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2380,12 +2380,12 @@
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“盛虹控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHENGHONG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG WEIQIAO PIONEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -2402,22 +2402,22 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>r172_basf</t>
+          <t>r178_statebankofindia</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>巴斯夫公司</t>
+          <t>印度国家银行</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>STATE BANK OF INDIA</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2435,12 +2435,12 @@
       <c r="I29" s="9" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴斯夫公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“印度国家银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BASF'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'STATE BANK OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -2457,22 +2457,22 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>r175_shandongweiqiaopioneeringgroup</t>
+          <t>r180_oilandnaturalgas</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>山东魏桥创业集团有限公司</t>
+          <t>印度石油天然气公司</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
+          <t>OIL &amp; NATURAL GAS</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2490,12 +2490,12 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“印度石油天然气公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG WEIQIAO PIONEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'OIL &amp; NATURAL GAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
@@ -2512,22 +2512,22 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>r178_statebankofindia</t>
+          <t>r187_xmxyg</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>印度国家银行</t>
+          <t>厦门象屿集团有限公司</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>STATE BANK OF INDIA</t>
+          <t>XMXYG</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2545,12 +2545,12 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度国家银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“厦门象屿集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE BANK OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'XMXYG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
@@ -2567,22 +2567,22 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>r180_oilandnaturalgas</t>
+          <t>r188_rtx</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>印度石油天然气公司</t>
+          <t>雷神技术公司</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>OIL &amp; NATURAL GAS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2600,12 +2600,12 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度石油天然气公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“雷神技术公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'OIL &amp; NATURAL GAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'RTX'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -2622,22 +2622,22 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>r187_xmxyg</t>
+          <t>r194_koc集团</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>厦门象屿集团有限公司</t>
+          <t>KOC集团</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>XMXYG</t>
+          <t>KOC集团</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2655,12 +2655,12 @@
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“厦门象屿集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“KOC集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'XMXYG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KOC集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -2677,22 +2677,22 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>r188_rtx</t>
+          <t>r197_rochegroup</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>雷神技术公司</t>
+          <t>瑞士罗氏公司</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ROCHE GROUP</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2710,12 +2710,12 @@
       <c r="I34" s="9" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“雷神技术公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“瑞士罗氏公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'RTX'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ROCHE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -2732,22 +2732,22 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>r194_koc集团</t>
+          <t>r200_bancobilbaovizcayaargentaria</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>KOC集团</t>
+          <t>西班牙对外银行</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>KOC集团</t>
+          <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2765,12 +2765,12 @@
       <c r="I35" s="9" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“KOC集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“西班牙对外银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KOC集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BANCO BILBAO VIZCAYA ARGENTARIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -2787,22 +2787,22 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>r197_rochegroup</t>
+          <t>r204_lloydsbankinggroup</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>瑞士罗氏公司</t>
+          <t>英国劳埃德银行集团</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>ROCHE GROUP</t>
+          <t>LLOYDS BANKING GROUP</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2820,12 +2820,12 @@
       <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“瑞士罗氏公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“英国劳埃德银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ROCHE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LLOYDS BANKING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
@@ -2842,22 +2842,22 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>r200_bancobilbaovizcayaargentaria</t>
+          <t>r205_deutschebank</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>西班牙对外银行</t>
+          <t>德意志银行</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
+          <t>DEUTSCHE BANK</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2875,12 +2875,12 @@
       <c r="I37" s="9" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“西班牙对外银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德意志银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANCO BILBAO VIZCAYA ARGENTARIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DEUTSCHE BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -2897,22 +2897,22 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>r204_lloydsbankinggroup</t>
+          <t>r210_unilever</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>英国劳埃德银行集团</t>
+          <t>联合利华</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>LLOYDS BANKING GROUP</t>
+          <t>UNILEVER</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2930,12 +2930,12 @@
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“英国劳埃德银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“联合利华”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LLOYDS BANKING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'UNILEVER'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -2952,22 +2952,22 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>r210_unilever</t>
+          <t>r213_jinnengholdinggroup</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>联合利华</t>
+          <t>晋能控股集团有限公司</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>UNILEVER</t>
+          <t>JINNENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2985,12 +2985,12 @@
       <c r="I39" s="9" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“联合利华”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“晋能控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'UNILEVER'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINNENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3007,22 +3007,22 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>r213_jinnengholdinggroup</t>
+          <t>r214_aluminumcorpofchina</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>214</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>晋能控股集团有限公司</t>
+          <t>中国铝业集团有限公司</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>JINNENG HOLDING GROUP</t>
+          <t>ALUMINUM CORP. OF CHINA</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3040,12 +3040,12 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“晋能控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国铝业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINNENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ALUMINUM CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -3062,22 +3062,22 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>r214_aluminumcorpofchina</t>
+          <t>r216_sberbank</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司</t>
+          <t>俄罗斯联邦储蓄银行</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>ALUMINUM CORP. OF CHINA</t>
+          <t>SBERBANK</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3095,12 +3095,12 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国铝业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯联邦储蓄银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ALUMINUM CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SBERBANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -3117,22 +3117,22 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>r216_sberbank</t>
+          <t>r218_progressive</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>俄罗斯联邦储蓄银行</t>
+          <t>前进保险公司</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>SBERBANK</t>
+          <t>PROGRESSIVE</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3150,12 +3150,12 @@
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯联邦储蓄银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“前进保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SBERBANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PROGRESSIVE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
@@ -3172,22 +3172,22 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>r218_progressive</t>
+          <t>r219_internationalbusinessmachines</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>前进保险公司</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>PROGRESSIVE</t>
+          <t>INTERNATIONAL BUSINESS MACHINES</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3205,12 +3205,12 @@
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“前进保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国际商业机器公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PROGRESSIVE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'INTERNATIONAL BUSINESS MACHINES'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
@@ -3227,22 +3227,22 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>r219_internationalbusinessmachines</t>
+          <t>r229_merck</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>国际商业机器公司</t>
+          <t>默沙东</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>INTERNATIONAL BUSINESS MACHINES</t>
+          <t>MERCK</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3260,12 +3260,12 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“国际商业机器公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“默沙东”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'INTERNATIONAL BUSINESS MACHINES'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MERCK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -3282,22 +3282,22 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>r022_industrialandcommercialbankofchina</t>
+          <t>r232_industrialbank</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>INDUSTRIAL &amp; COMMERCIAL BANK OF CHINA</t>
+          <t>INDUSTRIAL BANK</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3315,12 +3315,12 @@
       <c r="I45" s="9" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国工商银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“兴业银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'INDUSTRIAL &amp; COMMERCIAL BANK OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'INDUSTRIAL BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -3337,22 +3337,22 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>r220_nipponsteelcorporation</t>
+          <t>r233_poscoholdings</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>日本制铁集团公司</t>
+          <t>浦项制铁控股公司</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>NIPPON STEEL CORPORATION</t>
+          <t>POSCO HOLDINGS</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3370,12 +3370,12 @@
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“日本制铁集团公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浦项制铁控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NIPPON STEEL CORPORATION'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'POSCO HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>r229_merck</t>
+          <t>r238_chinahuanenggroup</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>默沙东</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>MERCK</t>
+          <t>CHINA HUANENG GROUP</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -3425,12 +3425,12 @@
       <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“默沙东”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国华能集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MERCK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUANENG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>r232_industrialbank</t>
+          <t>r239_chinaenergyengineeringgroup</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>中国能源建设集团有限公司</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>INDUSTRIAL BANK</t>
+          <t>CHINA ENERGY ENGINEERING GROUP</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -3480,12 +3480,12 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“兴业银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国能源建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'INDUSTRIAL BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ENERGY ENGINEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -3502,22 +3502,22 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>r233_poscoholdings</t>
+          <t>r024_glencore</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>浦项制铁控股公司</t>
+          <t>嘉能可</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>POSCO HOLDINGS</t>
+          <t>GLENCORE</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -3535,12 +3535,12 @@
       <c r="I49" s="9" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浦项制铁控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“嘉能可”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'POSCO HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GLENCORE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
@@ -3557,22 +3557,22 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>r239_chinaenergyengineeringgroup</t>
+          <t>r240_dongfengmotor</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>中国能源建设集团有限公司</t>
+          <t>东风汽车集团有限公司</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>CHINA ENERGY ENGINEERING GROUP</t>
+          <t>DONGFENG MOTOR</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -3590,12 +3590,12 @@
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国能源建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“东风汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ENERGY ENGINEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DONGFENG MOTOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
@@ -3612,22 +3612,22 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>r024_glencore</t>
+          <t>r242_publixsupermarkets</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>嘉能可</t>
+          <t>大众超级市场公司</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>GLENCORE</t>
+          <t>PUBLIX SUPER MARKETS</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -3645,12 +3645,12 @@
       <c r="I51" s="9" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“嘉能可”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“大众超级市场公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GLENCORE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PUBLIX SUPER MARKETS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
@@ -3667,22 +3667,22 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>r240_dongfengmotor</t>
+          <t>r243_zhejianghengyigroup</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>东风汽车集团有限公司</t>
+          <t>浙江恒逸集团有限公司</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>DONGFENG MOTOR</t>
+          <t>ZHEJIANG HENGYI GROUP</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -3700,12 +3700,12 @@
       <c r="I52" s="9" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“东风汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江恒逸集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DONGFENG MOTOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG HENGYI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
@@ -3722,22 +3722,22 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>r242_publixsupermarkets</t>
+          <t>r245_assicurazionigenerali</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>大众超级市场公司</t>
+          <t>意大利忠利保险公司</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>PUBLIX SUPER MARKETS</t>
+          <t>ASSICURAZIONI GENERALI</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3755,12 +3755,12 @@
       <c r="I53" s="9" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“大众超级市场公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“意大利忠利保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PUBLIX SUPER MARKETS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ASSICURAZIONI GENERALI'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -4107,22 +4107,22 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>r272_performancefoodgroup公司</t>
+          <t>r274_deutschebahn</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Performance Food Group公司</t>
+          <t>德国联邦铁路公司</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Performance Food Group公司</t>
+          <t>DEUTSCHE BAHN</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -4140,12 +4140,12 @@
       <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Performance Food Group公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国联邦铁路公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Performance Food Group公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DEUTSCHE BAHN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
@@ -4767,22 +4767,22 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>r294_bankofmontreal</t>
+          <t>r296_kb金融集团</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>蒙特利尔银行</t>
+          <t>KB金融集团</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>BANK OF MONTREAL</t>
+          <t>KB金融集团</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -4800,12 +4800,12 @@
       <c r="I72" s="9" t="inlineStr"/>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“蒙特利尔银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“KB金融集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF MONTREAL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KB金融集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
@@ -4822,22 +4822,22 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>r296_kb金融集团</t>
+          <t>r299_oracle</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>KB金融集团</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>KB金融集团</t>
+          <t>ORACLE</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -4855,12 +4855,12 @@
       <c r="I73" s="9" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“KB金融集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“甲骨文公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KB金融集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ORACLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
@@ -4877,22 +4877,22 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>r299_oracle</t>
+          <t>r003_stategrid</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>国家电网有限公司</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>ORACLE</t>
+          <t>STATE GRID</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -4910,12 +4910,12 @@
       <c r="I74" s="9" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“甲骨文公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国家电网有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ORACLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'STATE GRID'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
@@ -4932,22 +4932,22 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>r003_stategrid</t>
+          <t>r300_jinchuangroup</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>国家电网有限公司</t>
+          <t>金川集团股份有限公司</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>STATE GRID</t>
+          <t>JINCHUAN GROUP</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -4965,12 +4965,12 @@
       <c r="I75" s="9" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“国家电网有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“金川集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE GRID'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINCHUAN GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
@@ -4987,22 +4987,22 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>r030_chinaconstructionbank</t>
+          <t>r303_enterpriseproductspartners公司</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司</t>
+          <t>Enterprise Products Partners公司</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>CHINA CONSTRUCTION BANK</t>
+          <t>Enterprise Products Partners公司</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -5020,12 +5020,12 @@
       <c r="I76" s="9" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国建设银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enterprise Products Partners公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA CONSTRUCTION BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enterprise Products Partners公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr">
@@ -5042,22 +5042,22 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>r300_jinchuangroup</t>
+          <t>r304_capitalonefinancial</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司</t>
+          <t>第一资本金融公司</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>JINCHUAN GROUP</t>
+          <t>CAPITAL ONE FINANCIAL</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -5075,12 +5075,12 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“金川集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“第一资本金融公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINCHUAN GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CAPITAL ONE FINANCIAL'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
@@ -5097,22 +5097,22 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>r303_enterpriseproductspartners公司</t>
+          <t>r306_hdfc银行</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners公司</t>
+          <t>HDFC银行</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners公司</t>
+          <t>HDFC银行</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -5130,12 +5130,12 @@
       <c r="I78" s="9" t="inlineStr"/>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enterprise Products Partners公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“HDFC银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enterprise Products Partners公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HDFC银行'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
@@ -5152,22 +5152,22 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>r304_capitalonefinancial</t>
+          <t>r307_chinanationalbuildingmaterialgroup</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>第一资本金融公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>CAPITAL ONE FINANCIAL</t>
+          <t>CHINA NATIONAL BUILDING MATERIAL GROUP</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -5185,12 +5185,12 @@
       <c r="I79" s="9" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“第一资本金融公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国建材集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CAPITAL ONE FINANCIAL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL BUILDING MATERIAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
@@ -5207,22 +5207,22 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>r306_hdfc银行</t>
+          <t>r309_chinastateshipbuilding</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>HDFC银行</t>
+          <t>中国船舶集团有限公司</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>HDFC银行</t>
+          <t>CHINA STATE SHIPBUILDING</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -5240,12 +5240,12 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“HDFC银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国船舶集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HDFC银行'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA STATE SHIPBUILDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
@@ -5262,22 +5262,22 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>r307_chinanationalbuildingmaterialgroup</t>
+          <t>r312_landesbankbadenwürttemberg</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>德国巴登-符腾堡州银行</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL BUILDING MATERIAL GROUP</t>
+          <t>LANDESBANK BADEN-WÜRTTEMBERG</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -5295,12 +5295,12 @@
       <c r="I81" s="9" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国建材集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国巴登-符腾堡州银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL BUILDING MATERIAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LANDESBANK BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
@@ -5317,22 +5317,22 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>r309_chinastateshipbuilding</t>
+          <t>r314_jingyegroup</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>中国船舶集团有限公司</t>
+          <t>敬业集团有限公司</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>CHINA STATE SHIPBUILDING</t>
+          <t>JINGYE GROUP</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -5350,12 +5350,12 @@
       <c r="I82" s="9" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国船舶集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“敬业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA STATE SHIPBUILDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINGYE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L82" s="9" t="inlineStr">
@@ -5372,22 +5372,22 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>r312_landesbankbadenwürttemberg</t>
+          <t>r316_energiebadenwürttemberg</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>德国巴登-符腾堡州银行</t>
+          <t>巴登-符腾堡州能源公司</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>LANDESBANK BADEN-WÜRTTEMBERG</t>
+          <t>ENERGIE BADEN-WÜRTTEMBERG</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -5405,12 +5405,12 @@
       <c r="I83" s="9" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德国巴登-符腾堡州银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴登-符腾堡州能源公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LANDESBANK BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ENERGIE BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
@@ -5427,22 +5427,22 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>r314_jingyegroup</t>
+          <t>r321_hd现代公司</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>敬业集团有限公司</t>
+          <t>HD现代公司</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>JINGYE GROUP</t>
+          <t>HD现代公司</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -5460,12 +5460,12 @@
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“敬业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“HD现代公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINGYE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HD现代公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L84" s="9" t="inlineStr">
@@ -5482,22 +5482,22 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>r316_energiebadenwürttemberg</t>
+          <t>r325_softbankgroup</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>325</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>巴登-符腾堡州能源公司</t>
+          <t>软银集团</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>ENERGIE BADEN-WÜRTTEMBERG</t>
+          <t>SOFTBANK GROUP</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -5515,12 +5515,12 @@
       <c r="I85" s="9" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴登-符腾堡州能源公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“软银集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ENERGIE BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SOFTBANK GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L85" s="9" t="inlineStr">
@@ -5537,22 +5537,22 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>r321_hd现代公司</t>
+          <t>r328_américamóvil</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>HD现代公司</t>
+          <t>美洲电信</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>HD现代公司</t>
+          <t>AMÉRICA MÓVIL</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -5570,12 +5570,12 @@
       <c r="I86" s="9" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“HD现代公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美洲电信”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HD现代公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AMÉRICA MÓVIL'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr">
@@ -5592,22 +5592,22 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>r325_softbankgroup</t>
+          <t>r330_zhejiangcommunicationsinvestmentgroup</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>软银集团</t>
+          <t>浙江省交通投资集团有限公司</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>SOFTBANK GROUP</t>
+          <t>ZHEJIANG COMMUNICATIONS INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -5625,12 +5625,12 @@
       <c r="I87" s="9" t="inlineStr"/>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“软银集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江省交通投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SOFTBANK GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG COMMUNICATIONS INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L87" s="9" t="inlineStr">
@@ -5647,22 +5647,22 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>r328_américamóvil</t>
+          <t>r331_chinapacificinsurancegroup</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>美洲电信</t>
+          <t>中国太平洋保险(集团)股份有限公司</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>AMÉRICA MÓVIL</t>
+          <t>CHINA PACIFIC INSURANCE (GROUP)</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -5680,12 +5680,12 @@
       <c r="I88" s="9" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美洲电信”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国太平洋保险(集团)股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AMÉRICA MÓVIL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA PACIFIC INSURANCE (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L88" s="9" t="inlineStr">
@@ -5702,22 +5702,22 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>r330_zhejiangcommunicationsinvestmentgroup</t>
+          <t>r332_cocacola</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>332</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司</t>
+          <t>可口可乐公司</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>ZHEJIANG COMMUNICATIONS INVESTMENT GROUP</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -5735,12 +5735,12 @@
       <c r="I89" s="9" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江省交通投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“可口可乐公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG COMMUNICATIONS INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COCA-COLA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>r331_chinapacificinsurancegroup</t>
+          <t>r336_chinahuadian</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>中国太平洋保险(集团)股份有限公司</t>
+          <t>中国华电集团有限公司</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>CHINA PACIFIC INSURANCE (GROUP)</t>
+          <t>CHINA HUADIAN</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -5790,12 +5790,12 @@
       <c r="I90" s="9" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国太平洋保险(集团)股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国华电集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA PACIFIC INSURANCE (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUADIAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
@@ -5812,22 +5812,22 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>r332_cocacola</t>
+          <t>r337_créditmutuelgroup</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>可口可乐公司</t>
+          <t>法国国民互助信贷银行集团</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>CRÉDIT MUTUEL GROUP</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -5845,12 +5845,12 @@
       <c r="I91" s="9" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“可口可乐公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国国民互助信贷银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COCA-COLA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT MUTUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L91" s="9" t="inlineStr">
@@ -5867,22 +5867,22 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>r337_créditmutuelgroup</t>
+          <t>r338_msandad保险集团控股有限公司</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>法国国民互助信贷银行集团</t>
+          <t>MS&amp;AD保险集团控股有限公司</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>CRÉDIT MUTUEL GROUP</t>
+          <t>MS&amp;AD保险集团控股有限公司</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -5900,12 +5900,12 @@
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国国民互助信贷银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“MS&amp;AD保险集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT MUTUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MS&amp;AD保险集团控股有限公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr">
@@ -5922,22 +5922,22 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>r338_msandad保险集团控股有限公司</t>
+          <t>r340_susunconstructiongroup</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>340</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>MS&amp;AD保险集团控股有限公司</t>
+          <t>苏商建设集团有限公司</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>MS&amp;AD保险集团控股有限公司</t>
+          <t>SUSUN CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -5955,12 +5955,12 @@
       <c r="I93" s="9" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“MS&amp;AD保险集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“苏商建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MS&amp;AD保险集团控股有限公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SUSUN CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L93" s="9" t="inlineStr">
@@ -5977,22 +5977,22 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>r340_susunconstructiongroup</t>
+          <t>r341_sncfgroup</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>苏商建设集团有限公司</t>
+          <t>法国国营铁路集团</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>SUSUN CONSTRUCTION GROUP</t>
+          <t>SNCF GROUP</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -6010,12 +6010,12 @@
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“苏商建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国国营铁路集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SUSUN CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SNCF GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L94" s="9" t="inlineStr">
@@ -6032,22 +6032,22 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>r341_sncfgroup</t>
+          <t>r343_chinasouthindustriesgroup</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>343</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>法国国营铁路集团</t>
+          <t>中国兵器装备集团公司</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>SNCF GROUP</t>
+          <t>CHINA SOUTH INDUSTRIES GROUP</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -6065,12 +6065,12 @@
       <c r="I95" s="9" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国国营铁路集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国兵器装备集团公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SNCF GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA SOUTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
@@ -6087,22 +6087,22 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>r343_chinasouthindustriesgroup</t>
+          <t>r347_georgeweston</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>中国兵器装备集团公司</t>
+          <t>乔治威斯顿公司</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>CHINA SOUTH INDUSTRIES GROUP</t>
+          <t>GEORGE WESTON</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -6120,12 +6120,12 @@
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国兵器装备集团公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“乔治威斯顿公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA SOUTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GEORGE WESTON'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L96" s="9" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>r347_georgeweston</t>
+          <t>r351_chinaminshengbanking</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>乔治威斯顿公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>GEORGE WESTON</t>
+          <t>CHINA MINSHENG BANKING</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -6175,12 +6175,12 @@
       <c r="I97" s="9" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“乔治威斯顿公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国民生银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GEORGE WESTON'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA MINSHENG BANKING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L97" s="9" t="inlineStr">
@@ -6197,22 +6197,22 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>r351_chinaminshengbanking</t>
+          <t>r354_shanghaiconstructiongroup</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>上海建工集团股份有限公司</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>CHINA MINSHENG BANKING</t>
+          <t>SHANGHAI CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -6230,12 +6230,12 @@
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国民生银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海建工集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA MINSHENG BANKING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr">
@@ -6252,22 +6252,22 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>r354_shanghaiconstructiongroup</t>
+          <t>r355_lg化学公司</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>上海建工集团股份有限公司</t>
+          <t>LG化学公司</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI CONSTRUCTION GROUP</t>
+          <t>LG化学公司</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -6285,12 +6285,12 @@
       <c r="I99" s="9" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海建工集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“LG化学公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LG化学公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
@@ -6307,22 +6307,22 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>r355_lg化学公司</t>
+          <t>r360_unitedservicesautomobileassn</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>LG化学公司</t>
+          <t>联合服务汽车协会</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>LG化学公司</t>
+          <t>UNITED SERVICES AUTOMOBILE ASSN.</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -6340,12 +6340,12 @@
       <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“LG化学公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“联合服务汽车协会”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LG化学公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'UNITED SERVICES AUTOMOBILE ASSN.'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L100" s="9" t="inlineStr">
@@ -6362,22 +6362,22 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>r360_unitedservicesautomobileassn</t>
+          <t>r361_guangzhoumunicipalconstructiongroup</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>联合服务汽车协会</t>
+          <t>广州市建筑集团有限公司</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>UNITED SERVICES AUTOMOBILE ASSN.</t>
+          <t>GUANGZHOU MUNICIPAL CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -6395,12 +6395,12 @@
       <c r="I101" s="9" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“联合服务汽车协会”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州市建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'UNITED SERVICES AUTOMOBILE ASSN.'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU MUNICIPAL CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L101" s="9" t="inlineStr">
@@ -6417,22 +6417,22 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>r361_guangzhoumunicipalconstructiongroup</t>
+          <t>r362_generaldynamics</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>广州市建筑集团有限公司</t>
+          <t>通用动力</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU MUNICIPAL CONSTRUCTION GROUP</t>
+          <t>GENERAL DYNAMICS</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -6450,12 +6450,12 @@
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州市建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“通用动力”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU MUNICIPAL CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GENERAL DYNAMICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L102" s="9" t="inlineStr">
@@ -6472,22 +6472,22 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>r362_generaldynamics</t>
+          <t>r364_zijinmininggroup</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>通用动力</t>
+          <t>紫金矿业集团股份有限公司</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>GENERAL DYNAMICS</t>
+          <t>ZIJIN MINING GROUP</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -6505,12 +6505,12 @@
       <c r="I103" s="9" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“通用动力”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“紫金矿业集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GENERAL DYNAMICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZIJIN MINING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L103" s="9" t="inlineStr">
@@ -6527,22 +6527,22 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>r364_zijinmininggroup</t>
+          <t>r370_shenzheninvestmentholdings</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>紫金矿业集团股份有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>ZIJIN MINING GROUP</t>
+          <t>SHENZHEN INVESTMENT HOLDINGS</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -6560,12 +6560,12 @@
       <c r="I104" s="9" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“紫金矿业集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“深圳市投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZIJIN MINING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHENZHEN INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L104" s="9" t="inlineStr">
@@ -6582,22 +6582,22 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>r370_shenzheninvestmentholdings</t>
+          <t>r371_ansteelgroup</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>鞍钢集团有限公司</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>SHENZHEN INVESTMENT HOLDINGS</t>
+          <t>ANSTEEL GROUP</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -6615,12 +6615,12 @@
       <c r="I105" s="9" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“深圳市投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“鞍钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHENZHEN INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ANSTEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L105" s="9" t="inlineStr">
@@ -6637,22 +6637,22 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>r371_ansteelgroup</t>
+          <t>r372_hanwha</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>鞍钢集团有限公司</t>
+          <t>韩华集团</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>ANSTEEL GROUP</t>
+          <t>HANWHA</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -6670,12 +6670,12 @@
       <c r="I106" s="9" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“鞍钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“韩华集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ANSTEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANWHA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr">
@@ -6692,22 +6692,22 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>r372_hanwha</t>
+          <t>r373_usbancorp</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>韩华集团</t>
+          <t>美国合众银行</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>HANWHA</t>
+          <t>U.S. BANCORP</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -6725,12 +6725,12 @@
       <c r="I107" s="9" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“韩华集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国合众银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANWHA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'U.S. BANCORP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L107" s="9" t="inlineStr">
@@ -6747,22 +6747,22 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>r373_usbancorp</t>
+          <t>r377_thyssenkrupp</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>美国合众银行</t>
+          <t>蒂森克虏伯</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>U.S. BANCORP</t>
+          <t>THYSSENKRUPP</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -6780,12 +6780,12 @@
       <c r="I108" s="9" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国合众银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“蒂森克虏伯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'U.S. BANCORP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'THYSSENKRUPP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L108" s="9" t="inlineStr">
@@ -6802,22 +6802,22 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>r374_lufthansagroup</t>
+          <t>r038_bankofamerica</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>汉莎集团</t>
+          <t>美国银行</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>LUFTHANSA GROUP</t>
+          <t>BANK OF AMERICA</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -6835,12 +6835,12 @@
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“汉莎集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LUFTHANSA GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF AMERICA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr">
@@ -6857,22 +6857,22 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>r377_thyssenkrupp</t>
+          <t>r380_chinanationalnuclear</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>蒂森克虏伯</t>
+          <t>中国核工业集团有限公司</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP</t>
+          <t>CHINA NATIONAL NUCLEAR</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -6890,12 +6890,12 @@
       <c r="I110" s="9" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“蒂森克虏伯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国核工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'THYSSENKRUPP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL NUCLEAR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L110" s="9" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>r038_bankofamerica</t>
+          <t>r381_taikanginsurancegroup</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>美国银行</t>
+          <t>泰康保险集团股份有限公司</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>BANK OF AMERICA</t>
+          <t>TAIKANG INSURANCE GROUP</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -6945,12 +6945,12 @@
       <c r="I111" s="9" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“泰康保险集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF AMERICA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TAIKANG INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L111" s="9" t="inlineStr">
@@ -6967,22 +6967,22 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>r380_chinanationalnuclear</t>
+          <t>r382_northropgrumman</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>中国核工业集团有限公司</t>
+          <t>美国诺斯洛普格拉曼公司</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL NUCLEAR</t>
+          <t>NORTHROP GRUMMAN</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -7000,12 +7000,12 @@
       <c r="I112" s="9" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国核工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国诺斯洛普格拉曼公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL NUCLEAR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NORTHROP GRUMMAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L112" s="9" t="inlineStr">
@@ -7022,22 +7022,22 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>r381_taikanginsurancegroup</t>
+          <t>r383_jiangsushaganggroup</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>泰康保险集团股份有限公司</t>
+          <t>江苏沙钢集团有限公司</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>TAIKANG INSURANCE GROUP</t>
+          <t>JIANGSU SHAGANG GROUP</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -7055,12 +7055,12 @@
       <c r="I113" s="9" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“泰康保险集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“江苏沙钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TAIKANG INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JIANGSU SHAGANG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L113" s="9" t="inlineStr">
@@ -7077,22 +7077,22 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>r382_northropgrumman</t>
+          <t>r389_dollargeneral公司</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>美国诺斯洛普格拉曼公司</t>
+          <t>Dollar General公司</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>NORTHROP GRUMMAN</t>
+          <t>Dollar General公司</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -7110,12 +7110,12 @@
       <c r="I114" s="9" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国诺斯洛普格拉曼公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Dollar General公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NORTHROP GRUMMAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Dollar General公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L114" s="9" t="inlineStr">
@@ -7132,22 +7132,22 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>r383_jiangsushaganggroup</t>
+          <t>r390_cenovusenergy公司</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>江苏沙钢集团有限公司</t>
+          <t>Cenovus Energy公司</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>JIANGSU SHAGANG GROUP</t>
+          <t>Cenovus Energy公司</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -7165,12 +7165,12 @@
       <c r="I115" s="9" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“江苏沙钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Cenovus Energy公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JIANGSU SHAGANG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Cenovus Energy公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L115" s="9" t="inlineStr">
@@ -7187,22 +7187,22 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>r389_dollargeneral公司</t>
+          <t>r393_fairfaxfinancialholdings</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>393</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Dollar General公司</t>
+          <t>加拿大枫信金融控股公司</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Dollar General公司</t>
+          <t>FAIRFAX FINANCIAL HOLDINGS</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -7220,12 +7220,12 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Dollar General公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大枫信金融控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Dollar General公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'FAIRFAX FINANCIAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L116" s="9" t="inlineStr">
@@ -7242,22 +7242,22 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>r390_cenovusenergy公司</t>
+          <t>r394_guangzhouindustrialinvestmentholdings</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>394</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Cenovus Energy公司</t>
+          <t>广州工业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Cenovus Energy公司</t>
+          <t>GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -7275,12 +7275,12 @@
       <c r="I117" s="9" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Cenovus Energy公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州工业投资控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Cenovus Energy公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L117" s="9" t="inlineStr">
@@ -7297,22 +7297,22 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>r393_fairfaxfinancialholdings</t>
+          <t>r040_elevancehealth公司</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>加拿大枫信金融控股公司</t>
+          <t>Elevance Health公司</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>FAIRFAX FINANCIAL HOLDINGS</t>
+          <t>Elevance Health公司</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -7330,12 +7330,12 @@
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“加拿大枫信金融控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Elevance Health公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FAIRFAX FINANCIAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Elevance Health公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L118" s="9" t="inlineStr">
@@ -7352,22 +7352,22 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>r394_guangzhouindustrialinvestmentholdings</t>
+          <t>r402_hangzhouindustrialinvestmentgroup</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>402</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>广州工业投资控股集团有限公司</t>
+          <t>杭州市实业投资集团有限公司</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS</t>
+          <t>HANGZHOU INDUSTRIAL INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -7385,12 +7385,12 @@
       <c r="I119" s="9" t="inlineStr"/>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州工业投资控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“杭州市实业投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU INDUSTRIAL INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L119" s="9" t="inlineStr">
@@ -7407,22 +7407,22 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>r040_elevancehealth公司</t>
+          <t>r404_dzbank</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Elevance Health公司</t>
+          <t>德国中央合作银行</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Elevance Health公司</t>
+          <t>DZ BANK</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -7440,12 +7440,12 @@
       <c r="I120" s="9" t="inlineStr"/>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Elevance Health公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国中央合作银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Elevance Health公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DZ BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L120" s="9" t="inlineStr">
@@ -7462,22 +7462,22 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>r402_hangzhouindustrialinvestmentgroup</t>
+          <t>r405_gs加德士</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>405</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>杭州市实业投资集团有限公司</t>
+          <t>GS加德士</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>HANGZHOU INDUSTRIAL INVESTMENT GROUP</t>
+          <t>GS加德士</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -7495,12 +7495,12 @@
       <c r="I121" s="9" t="inlineStr"/>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“杭州市实业投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“GS加德士”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU INDUSTRIAL INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GS加德士'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L121" s="9" t="inlineStr">
@@ -7517,22 +7517,22 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>r404_dzbank</t>
+          <t>r408_x5零售集团</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>408</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>德国中央合作银行</t>
+          <t>X5零售集团</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>DZ BANK</t>
+          <t>X5零售集团</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -7550,12 +7550,12 @@
       <c r="I122" s="9" t="inlineStr"/>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德国中央合作银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“X5零售集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DZ BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'X5零售集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L122" s="9" t="inlineStr">
@@ -7572,22 +7572,22 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>r405_gs加德士</t>
+          <t>r410_hangzhouironandsteelgroup</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>410</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>GS加德士</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>GS加德士</t>
+          <t>HANGZHOU IRON AND STEEL GROUP</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -7605,12 +7605,12 @@
       <c r="I123" s="9" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“GS加德士”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“杭州钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GS加德士'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU IRON AND STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L123" s="9" t="inlineStr">
@@ -7627,22 +7627,22 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>r408_x5零售集团</t>
+          <t>r411_shanghaipharmaceuticalsholding</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>411</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>X5零售集团</t>
+          <t>上海医药集团股份有限公司</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>X5零售集团</t>
+          <t>SHANGHAI PHARMACEUTICALS HOLDING</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -7660,12 +7660,12 @@
       <c r="I124" s="9" t="inlineStr"/>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“X5零售集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海医药集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'X5零售集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PHARMACEUTICALS HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L124" s="9" t="inlineStr">
@@ -7682,22 +7682,22 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>r410_hangzhouironandsteelgroup</t>
+          <t>r412_shandonghispeedgroup</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>412</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>HANGZHOU IRON AND STEEL GROUP</t>
+          <t>SHANDONG HI-SPEED GROUP</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -7715,12 +7715,12 @@
       <c r="I125" s="9" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“杭州钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东高速集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU IRON AND STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG HI-SPEED GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L125" s="9" t="inlineStr">
@@ -7737,22 +7737,22 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>r411_shanghaipharmaceuticalsholding</t>
+          <t>r414_guangdongguangxinholdingsgroup</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>414</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>上海医药集团股份有限公司</t>
+          <t>广东省广新控股集团有限公司</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI PHARMACEUTICALS HOLDING</t>
+          <t>GUANGDONG GUANGXIN HOLDINGS GROUP</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -7770,12 +7770,12 @@
       <c r="I126" s="9" t="inlineStr"/>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海医药集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广东省广新控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PHARMACEUTICALS HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGDONG GUANGXIN HOLDINGS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L126" s="9" t="inlineStr">
@@ -7792,22 +7792,22 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>r412_shandonghispeedgroup</t>
+          <t>r417_guangzhoupharmaceuticalholdings</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>417</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>广州医药集团有限公司</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>SHANDONG HI-SPEED GROUP</t>
+          <t>GUANGZHOU PHARMACEUTICAL HOLDINGS</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -7825,12 +7825,12 @@
       <c r="I127" s="9" t="inlineStr"/>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东高速集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州医药集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG HI-SPEED GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU PHARMACEUTICAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L127" s="9" t="inlineStr">
@@ -7847,22 +7847,22 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>r414_guangdongguangxinholdingsgroup</t>
+          <t>r419_mapfregroup</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>419</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>广东省广新控股集团有限公司</t>
+          <t>曼福集团</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>GUANGDONG GUANGXIN HOLDINGS GROUP</t>
+          <t>MAPFRE GROUP</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
@@ -7880,12 +7880,12 @@
       <c r="I128" s="9" t="inlineStr"/>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广东省广新控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“曼福集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGDONG GUANGXIN HOLDINGS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MAPFRE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L128" s="9" t="inlineStr">
@@ -7902,22 +7902,22 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>r417_guangzhoupharmaceuticalholdings</t>
+          <t>r420_cfe公司</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>420</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>广州医药集团有限公司</t>
+          <t>CFE公司</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU PHARMACEUTICAL HOLDINGS</t>
+          <t>CFE公司</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -7935,12 +7935,12 @@
       <c r="I129" s="9" t="inlineStr"/>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州医药集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“CFE公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU PHARMACEUTICAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CFE公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L129" s="9" t="inlineStr">
@@ -7957,22 +7957,22 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>r419_mapfregroup</t>
+          <t>r043_chinarailwayconstruction</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>曼福集团</t>
+          <t>中国铁道建筑集团有限公司</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>MAPFRE GROUP</t>
+          <t>CHINA RAILWAY CONSTRUCTION</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="I130" s="9" t="inlineStr"/>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“曼福集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国铁道建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MAPFRE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA RAILWAY CONSTRUCTION'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L130" s="9" t="inlineStr">
@@ -8012,22 +8012,22 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>r420_cfe公司</t>
+          <t>r430_usfoodsholding公司</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>430</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>CFE公司</t>
+          <t>US Foods Holding公司</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>CFE公司</t>
+          <t>US Foods Holding公司</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -8045,12 +8045,12 @@
       <c r="I131" s="9" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“CFE公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“US Foods Holding公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CFE公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'US Foods Holding公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L131" s="9" t="inlineStr">
@@ -8067,22 +8067,22 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>r043_chinarailwayconstruction</t>
+          <t>r432_migros集团</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>432</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>中国铁道建筑集团有限公司</t>
+          <t>Migros集团</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>CHINA RAILWAY CONSTRUCTION</t>
+          <t>Migros集团</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -8100,12 +8100,12 @@
       <c r="I132" s="9" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国铁道建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Migros集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA RAILWAY CONSTRUCTION'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Migros集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L132" s="9" t="inlineStr">
@@ -8122,22 +8122,22 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>r430_usfoodsholding公司</t>
+          <t>r435_chinaelectronics</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>435</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>US Foods Holding公司</t>
+          <t>中国电子信息产业集团有限公司</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>US Foods Holding公司</t>
+          <t>CHINA ELECTRONICS</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -8155,12 +8155,12 @@
       <c r="I133" s="9" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“US Foods Holding公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国电子信息产业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'US Foods Holding公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L133" s="9" t="inlineStr">
@@ -8177,22 +8177,22 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>r432_migros集团</t>
+          <t>r436_shudaoinvestmentgroup</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>436</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Migros集团</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Migros集团</t>
+          <t>SHUDAO INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -8210,12 +8210,12 @@
       <c r="I134" s="9" t="inlineStr"/>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Migros集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“蜀道投资集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Migros集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHUDAO INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L134" s="9" t="inlineStr">
@@ -8232,22 +8232,22 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>r435_chinaelectronics</t>
+          <t>r437_chinanationalcoalgroup</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>437</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>中国电子信息产业集团有限公司</t>
+          <t>中国中煤能源集团有限公司</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>CHINA ELECTRONICS</t>
+          <t>CHINA NATIONAL COAL GROUP</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -8265,12 +8265,12 @@
       <c r="I135" s="9" t="inlineStr"/>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国电子信息产业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国中煤能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L135" s="9" t="inlineStr">
@@ -8287,22 +8287,22 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>r436_shudaoinvestmentgroup</t>
+          <t>r438_tonglingnonferrousmetalsgroup</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>铜陵有色金属集团控股有限公司</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>SHUDAO INVESTMENT GROUP</t>
+          <t>TONGLING NONFERROUS METALS GROUP</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
@@ -8320,12 +8320,12 @@
       <c r="I136" s="9" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“蜀道投资集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“铜陵有色金属集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHUDAO INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TONGLING NONFERROUS METALS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L136" s="9" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>r437_chinanationalcoalgroup</t>
+          <t>r439_ckhutchisonholdings</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>439</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>中国中煤能源集团有限公司</t>
+          <t>长江和记实业有限公司</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL COAL GROUP</t>
+          <t>CK HUTCHISON HOLDINGS</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -8375,12 +8375,12 @@
       <c r="I137" s="9" t="inlineStr"/>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国中煤能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“长江和记实业有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CK HUTCHISON HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L137" s="9" t="inlineStr">
@@ -8397,22 +8397,22 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>r438_tonglingnonferrousmetalsgroup</t>
+          <t>r442_pddholdings</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>442</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>铜陵有色金属集团控股有限公司</t>
+          <t>拼多多控股公司</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>TONGLING NONFERROUS METALS GROUP</t>
+          <t>PDD HOLDINGS</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -8430,12 +8430,12 @@
       <c r="I138" s="9" t="inlineStr"/>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“铜陵有色金属集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“拼多多控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TONGLING NONFERROUS METALS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PDD HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L138" s="9" t="inlineStr">
@@ -8452,22 +8452,22 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>r439_ckhutchisonholdings</t>
+          <t>r447_nucor</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>447</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>长江和记实业有限公司</t>
+          <t>纽柯</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>CK HUTCHISON HOLDINGS</t>
+          <t>NUCOR</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -8485,12 +8485,12 @@
       <c r="I139" s="9" t="inlineStr"/>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“长江和记实业有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“纽柯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CK HUTCHISON HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NUCOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L139" s="9" t="inlineStr">
@@ -8507,22 +8507,22 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>r442_pddholdings</t>
+          <t>r452_shanghaidelongsteelgroup</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>452</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>拼多多控股公司</t>
+          <t>上海德龙钢铁集团有限公司</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>PDD HOLDINGS</t>
+          <t>SHANGHAI DELONG STEEL GROUP</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -8540,12 +8540,12 @@
       <c r="I140" s="9" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“拼多多控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海德龙钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PDD HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI DELONG STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L140" s="9" t="inlineStr">
@@ -8562,22 +8562,22 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>r447_nucor</t>
+          <t>r458_beijingjianlongheavyindustrygroup</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>458</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>纽柯</t>
+          <t>北京建龙重工集团有限公司</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>NUCOR</t>
+          <t>BEIJING JIANLONG HEAVY INDUSTRY GROUP</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -8595,12 +8595,12 @@
       <c r="I141" s="9" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“纽柯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“北京建龙重工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NUCOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BEIJING JIANLONG HEAVY INDUSTRY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L141" s="9" t="inlineStr">
@@ -8617,22 +8617,22 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>r452_shanghaidelongsteelgroup</t>
+          <t>r460_shaanxiconstructionengineeringholding</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>460</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>上海德龙钢铁集团有限公司</t>
+          <t>陕西建工控股集团有限公司</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI DELONG STEEL GROUP</t>
+          <t>SHAANXI CONSTRUCTION ENGINEERING HOLDING</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -8650,12 +8650,12 @@
       <c r="I142" s="9" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海德龙钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“陕西建工控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI DELONG STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI CONSTRUCTION ENGINEERING HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L142" s="9" t="inlineStr">
@@ -8672,22 +8672,22 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>r458_beijingjianlongheavyindustrygroup</t>
+          <t>r465_cpc</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>465</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>北京建龙重工集团有限公司</t>
+          <t>台湾中油股份有限公司</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>BEIJING JIANLONG HEAVY INDUSTRY GROUP</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -8705,12 +8705,12 @@
       <c r="I143" s="9" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“北京建龙重工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“台湾中油股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BEIJING JIANLONG HEAVY INDUSTRY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CPC'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L143" s="9" t="inlineStr">
@@ -8727,22 +8727,22 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>r460_shaanxiconstructionengineeringholding</t>
+          <t>r471_shanxicokingcoalgroup</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>471</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>陕西建工控股集团有限公司</t>
+          <t>山西焦煤集团有限责任公司</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>SHAANXI CONSTRUCTION ENGINEERING HOLDING</t>
+          <t>SHANXI COKING COAL GROUP</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -8760,12 +8760,12 @@
       <c r="I144" s="9" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“陕西建工控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山西焦煤集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI CONSTRUCTION ENGINEERING HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANXI COKING COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L144" s="9" t="inlineStr">
@@ -8782,22 +8782,22 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>r465_cpc</t>
+          <t>r472_guangxiinvestmentgroup</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>472</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>台湾中油股份有限公司</t>
+          <t>广西投资集团有限公司</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>GUANGXI INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -8815,12 +8815,12 @@
       <c r="I145" s="9" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“台湾中油股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广西投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CPC'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGXI INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr">
@@ -8837,22 +8837,22 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>r471_shanxicokingcoalgroup</t>
+          <t>r476_powercorpofcanada</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>476</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>山西焦煤集团有限责任公司</t>
+          <t>加拿大鲍尔集团</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>SHANXI COKING COAL GROUP</t>
+          <t>POWER CORP. OF CANADA</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -8870,12 +8870,12 @@
       <c r="I146" s="9" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山西焦煤集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大鲍尔集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANXI COKING COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'POWER CORP. OF CANADA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L146" s="9" t="inlineStr">
@@ -8892,22 +8892,22 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>r472_guangxiinvestmentgroup</t>
+          <t>r483_chinanationalaviationfuelgroup</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>483</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司</t>
+          <t>中国航空油料集团有限公司</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>GUANGXI INVESTMENT GROUP</t>
+          <t>CHINA NATIONAL AVIATION FUEL GROUP</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -8925,12 +8925,12 @@
       <c r="I147" s="9" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广西投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国航空油料集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGXI INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL AVIATION FUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr">
@@ -8947,22 +8947,22 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>r476_powercorpofcanada</t>
+          <t>r488_luxshareprecisionindustry</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>488</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>加拿大鲍尔集团</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>POWER CORP. OF CANADA</t>
+          <t>LUXSHARE PRECISION INDUSTRY</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
@@ -8980,12 +8980,12 @@
       <c r="I148" s="9" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“加拿大鲍尔集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“立讯精密工业股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'POWER CORP. OF CANADA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LUXSHARE PRECISION INDUSTRY'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L148" s="9" t="inlineStr">
@@ -9002,22 +9002,22 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>r483_chinanationalaviationfuelgroup</t>
+          <t>r490_visa公司</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>490</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>中国航空油料集团有限公司</t>
+          <t>Visa公司</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL AVIATION FUEL GROUP</t>
+          <t>Visa公司</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
@@ -9035,12 +9035,12 @@
       <c r="I149" s="9" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国航空油料集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Visa公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL AVIATION FUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Visa公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L149" s="9" t="inlineStr">
@@ -9057,22 +9057,22 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>r488_luxshareprecisionindustry</t>
+          <t>r496_airfranceklmgroup</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>496</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>法国航空－荷兰皇家航空集团</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>LUXSHARE PRECISION INDUSTRY</t>
+          <t>AIR FRANCE-KLM GROUP</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -9090,12 +9090,12 @@
       <c r="I150" s="9" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“立讯精密工业股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国航空－荷兰皇家航空集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LUXSHARE PRECISION INDUSTRY'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AIR FRANCE-KLM GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr">
@@ -9112,22 +9112,22 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>r490_visa公司</t>
+          <t>r497_enbridge公司</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>497</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Visa公司</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Visa公司</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -9145,12 +9145,12 @@
       <c r="I151" s="9" t="inlineStr"/>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Visa公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Visa公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L151" s="9" t="inlineStr">
@@ -9167,22 +9167,22 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>r496_airfranceklmgroup</t>
+          <t>r499_enbridge公司</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>499</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>法国航空－荷兰皇家航空集团</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>AIR FRANCE-KLM GROUP</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -9200,12 +9200,12 @@
       <c r="I152" s="9" t="inlineStr"/>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国航空－荷兰皇家航空集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AIR FRANCE-KLM GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L152" s="9" t="inlineStr">
@@ -9222,22 +9222,22 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>r497_enbridge公司</t>
+          <t>r005_sinopecgroup</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Enbridge公司</t>
+          <t>中国石油化工集团有限公司</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Enbridge公司</t>
+          <t>SINOPEC GROUP</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="I153" s="9" t="inlineStr"/>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国石油化工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SINOPEC GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L153" s="9" t="inlineStr">
@@ -9277,22 +9277,22 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>r499_enbridge公司</t>
+          <t>r051_kroger</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>Enbridge公司</t>
+          <t>克罗格</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Enbridge公司</t>
+          <t>KROGER</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
@@ -9310,12 +9310,12 @@
       <c r="I154" s="9" t="inlineStr"/>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“克罗格”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KROGER'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L154" s="9" t="inlineStr">
@@ -9332,22 +9332,22 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>r005_sinopecgroup</t>
+          <t>r058_fanniemae</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>中国石油化工集团有限公司</t>
+          <t>房利美</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>SINOPEC GROUP</t>
+          <t>FANNIE MAE</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -9365,12 +9365,12 @@
       <c r="I155" s="9" t="inlineStr"/>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油化工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“房利美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SINOPEC GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'FANNIE MAE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L155" s="9" t="inlineStr">
@@ -9387,22 +9387,22 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>r051_kroger</t>
+          <t>r059_chinalifeinsurance</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>克罗格</t>
+          <t>中国人寿保险（集团）公司</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>KROGER</t>
+          <t>CHINA LIFE INSURANCE</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -9420,12 +9420,12 @@
       <c r="I156" s="9" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“克罗格”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国人寿保险（集团）公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KROGER'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA LIFE INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L156" s="9" t="inlineStr">
@@ -9442,22 +9442,22 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>r056_chinanationaloffshoreoil</t>
+          <t>r006_chinanationalpetroleum</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>中国海洋石油集团有限公司</t>
+          <t>中国石油天然气集团有限公司</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL OFFSHORE OIL</t>
+          <t>CHINA NATIONAL PETROLEUM</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -9475,12 +9475,12 @@
       <c r="I157" s="9" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国海洋石油集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国石油天然气集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL OFFSHORE OIL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL PETROLEUM'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L157" s="9" t="inlineStr">
@@ -9497,22 +9497,22 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>r058_fanniemae</t>
+          <t>r064_bnpparibas</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>房利美</t>
+          <t>法国巴黎银行</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>FANNIE MAE</t>
+          <t>BNP PARIBAS</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
@@ -9530,12 +9530,12 @@
       <c r="I158" s="9" t="inlineStr"/>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“房利美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国巴黎银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FANNIE MAE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BNP PARIBAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L158" s="9" t="inlineStr">
@@ -9552,22 +9552,22 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>r059_chinalifeinsurance</t>
+          <t>r075_shandongenergygroup</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>中国人寿保险（集团）公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>CHINA LIFE INSURANCE</t>
+          <t>SHANDONG ENERGY GROUP</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -9585,12 +9585,12 @@
       <c r="I159" s="9" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国人寿保险（集团）公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA LIFE INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG ENERGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L159" s="9" t="inlineStr">
@@ -9607,22 +9607,22 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>r006_chinanationalpetroleum</t>
+          <t>r076_comcast</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司</t>
+          <t>美国康卡斯特电信公司</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL PETROLEUM</t>
+          <t>COMCAST</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
@@ -9640,12 +9640,12 @@
       <c r="I160" s="9" t="inlineStr"/>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油天然气集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国康卡斯特电信公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL PETROLEUM'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COMCAST'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L160" s="9" t="inlineStr">
@@ -9662,22 +9662,22 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>r069_chinaminmetals</t>
+          <t>r080_wellsfargo</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>中国五矿集团有限公司</t>
+          <t>美国富国银行</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>CHINA MINMETALS</t>
+          <t>WELLS FARGO</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -9695,12 +9695,12 @@
       <c r="I161" s="9" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国五矿集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国富国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA MINMETALS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'WELLS FARGO'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L161" s="9" t="inlineStr">
@@ -9717,22 +9717,22 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>r075_shandongenergygroup</t>
+          <t>r081_hengligroup</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>恒力集团有限公司</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>SHANDONG ENERGY GROUP</t>
+          <t>HENGLI GROUP</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -9750,12 +9750,12 @@
       <c r="I162" s="9" t="inlineStr"/>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG ENERGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HENGLI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L162" s="9" t="inlineStr">
@@ -9772,22 +9772,22 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>r076_comcast</t>
+          <t>r083_chinapostgroup</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>美国康卡斯特电信公司</t>
+          <t>中国邮政集团有限公司</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>COMCAST</t>
+          <t>CHINA POST GROUP</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
@@ -9805,12 +9805,12 @@
       <c r="I163" s="9" t="inlineStr"/>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国康卡斯特电信公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COMCAST'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA POST GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L163" s="9" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>r078_chinasouthernpowergrid</t>
+          <t>r087_goldmansachsgroup</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>高盛集团</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>CHINA SOUTHERN POWER GRID</t>
+          <t>GOLDMAN SACHS GROUP</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -9860,12 +9860,12 @@
       <c r="I164" s="9" t="inlineStr"/>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国南方电网有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“高盛集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA SOUTHERN POWER GRID'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GOLDMAN SACHS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L164" s="9" t="inlineStr">
@@ -9882,22 +9882,22 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>r080_wellsfargo</t>
+          <t>r088_freddiemac</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>美国富国银行</t>
+          <t>房地美</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>WELLS FARGO</t>
+          <t>FREDDIE MAC</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -9915,12 +9915,12 @@
       <c r="I165" s="9" t="inlineStr"/>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国富国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“房地美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'WELLS FARGO'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'FREDDIE MAC'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L165" s="9" t="inlineStr">
@@ -9937,22 +9937,22 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>r081_hengligroup</t>
+          <t>r009_berkshirehathaway</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>恒力集团有限公司</t>
+          <t>伯克希尔－哈撒韦公司</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>HENGLI GROUP</t>
+          <t>BERKSHIRE HATHAWAY</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -9970,12 +9970,12 @@
       <c r="I166" s="9" t="inlineStr"/>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“伯克希尔－哈撒韦公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HENGLI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BERKSHIRE HATHAWAY'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L166" s="9" t="inlineStr">
@@ -9992,22 +9992,22 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>r083_chinapostgroup</t>
+          <t>r092_humana</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司</t>
+          <t>哈门那公司</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>CHINA POST GROUP</t>
+          <t>HUMANA</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -10025,12 +10025,12 @@
       <c r="I167" s="9" t="inlineStr"/>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“哈门那公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA POST GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HUMANA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L167" s="9" t="inlineStr">
@@ -10047,22 +10047,22 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>r087_goldmansachsgroup</t>
+          <t>r094_statefarminsurance</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>高盛集团</t>
+          <t>州立农业保险公司</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>GOLDMAN SACHS GROUP</t>
+          <t>STATE FARM INSURANCE</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -10080,12 +10080,12 @@
       <c r="I168" s="9" t="inlineStr"/>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“高盛集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“州立农业保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GOLDMAN SACHS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'STATE FARM INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L168" s="9" t="inlineStr">
@@ -10102,22 +10102,22 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>r088_freddiemac</t>
+          <t>r095_lifeinsurancecorpofindia</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>房地美</t>
+          <t>印度人寿保险公司</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>FREDDIE MAC</t>
+          <t>LIFE INSURANCE CORP. OF INDIA</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -10135,12 +10135,12 @@
       <c r="I169" s="9" t="inlineStr"/>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“房地美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“印度人寿保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FREDDIE MAC'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LIFE INSURANCE CORP. OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L169" s="9" t="inlineStr">
@@ -10157,22 +10157,22 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>r009_berkshirehathaway</t>
+          <t>r099_petrobras</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>伯克希尔－哈撒韦公司</t>
+          <t>巴西国家石油公司</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>BERKSHIRE HATHAWAY</t>
+          <t>PETROBRAS</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
@@ -10190,12 +10190,12 @@
       <c r="I170" s="9" t="inlineStr"/>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“伯克希尔－哈撒韦公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴西国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BERKSHIRE HATHAWAY'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PETROBRAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L170" s="9" t="inlineStr">
@@ -10209,228 +10209,8 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="9" t="inlineStr">
-        <is>
-          <t>r092_humana</t>
-        </is>
-      </c>
-      <c r="B171" s="9" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>哈门那公司</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>HUMANA</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr"/>
-      <c r="H171" s="4" t="inlineStr"/>
-      <c r="I171" s="9" t="inlineStr"/>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“哈门那公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HUMANA'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L171" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M171" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="9" t="inlineStr">
-        <is>
-          <t>r094_statefarminsurance</t>
-        </is>
-      </c>
-      <c r="B172" s="9" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>州立农业保险公司</t>
-        </is>
-      </c>
-      <c r="D172" s="9" t="inlineStr">
-        <is>
-          <t>STATE FARM INSURANCE</t>
-        </is>
-      </c>
-      <c r="E172" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr"/>
-      <c r="H172" s="4" t="inlineStr"/>
-      <c r="I172" s="9" t="inlineStr"/>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“州立农业保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE FARM INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L172" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M172" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>r095_lifeinsurancecorpofindia</t>
-        </is>
-      </c>
-      <c r="B173" s="9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C173" s="9" t="inlineStr">
-        <is>
-          <t>印度人寿保险公司</t>
-        </is>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>LIFE INSURANCE CORP. OF INDIA</t>
-        </is>
-      </c>
-      <c r="E173" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr"/>
-      <c r="H173" s="4" t="inlineStr"/>
-      <c r="I173" s="9" t="inlineStr"/>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度人寿保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K173" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LIFE INSURANCE CORP. OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L173" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M173" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="9" t="inlineStr">
-        <is>
-          <t>r099_petrobras</t>
-        </is>
-      </c>
-      <c r="B174" s="9" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>巴西国家石油公司</t>
-        </is>
-      </c>
-      <c r="D174" s="9" t="inlineStr">
-        <is>
-          <t>PETROBRAS</t>
-        </is>
-      </c>
-      <c r="E174" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="inlineStr"/>
-      <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="9" t="inlineStr"/>
-      <c r="J174" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴西国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K174" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PETROBRAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L174" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M174" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:M174"/>
+  <autoFilter ref="A3:M170"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>

--- a/assets/downloads/world500_unmatched_diagnosis.xlsx
+++ b/assets/downloads/world500_unmatched_diagnosis.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'分类汇总'!$A$3:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'174条诊断总表'!$A$3:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'174条诊断总表'!$A$3:$M$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +557,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>167 条未匹配诊断表</t>
+          <t>147 条未匹配诊断表</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -589,7 +589,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>本表仅针对 world500_match_review.csv 中当前 review_decision 为空的 167 条未决匹配进行诊断。</t>
+          <t>本表仅针对 world500_match_review.csv 中当前 review_decision 为空的 147 条未决匹配进行诊断。</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -645,7 +645,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>未决匹配总数：167</t>
+          <t>未决匹配总数：147</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>库存文件总数：396</t>
+          <t>库存文件总数：415</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -669,7 +669,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>生成时间：2026-04-15 18:50:53</t>
+          <t>生成时间：2026-04-18 11:14:36</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -722,7 +722,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>本页汇总 167 条未决匹配在四种诊断类别下的数量分布。</t>
+          <t>本页汇总 147 条未决匹配在四种诊断类别下的数量分布。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1357,22 +1357,22 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>r100_sk集团</t>
+          <t>r102_gazprom</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>SK集团</t>
+          <t>俄罗斯天然气工业股份公司</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>SK集团</t>
+          <t>GAZPROM</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1390,12 +1390,12 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“SK集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯天然气工业股份公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SK集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GAZPROM'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -1412,22 +1412,22 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>r102_gazprom</t>
+          <t>r106_cofco</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>俄罗斯天然气工业股份公司</t>
+          <t>中粮集团有限公司</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>GAZPROM</t>
+          <t>COFCO</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1445,12 +1445,12 @@
       <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯天然气工业股份公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中粮集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GAZPROM'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COFCO'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1467,22 +1467,22 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>r103_huaweiinvestmentandholding</t>
+          <t>r109_pemex</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司</t>
+          <t>墨西哥石油公司</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>HUAWEI INVESTMENT &amp; HOLDING</t>
+          <t>PEMEX</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1500,12 +1500,12 @@
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“华为投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“墨西哥石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HUAWEI INVESTMENT &amp; HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PEMEX'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -1522,22 +1522,22 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>r106_cofco</t>
+          <t>r118_créditagricole</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>中粮集团有限公司</t>
+          <t>法国农业信贷银行</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>COFCO</t>
+          <t>CRÉDIT AGRICOLE</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1555,12 +1555,12 @@
       <c r="I13" s="9" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中粮集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国农业信贷银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COFCO'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT AGRICOLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -1577,22 +1577,22 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>r109_pemex</t>
+          <t>r138_zhejiangrongshengholdinggroup</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>墨西哥石油公司</t>
+          <t>浙江荣盛控股集团有限公司</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>PEMEX</t>
+          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1610,12 +1610,12 @@
       <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“墨西哥石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PEMEX'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG RONGSHENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -1632,22 +1632,22 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>r118_créditagricole</t>
+          <t>r142_xiamenitgholdinggroup</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>法国农业信贷银行</t>
+          <t>厦门国贸控股集团有限公司</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>CRÉDIT AGRICOLE</t>
+          <t>XIAMEN ITG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1665,12 +1665,12 @@
       <c r="I15" s="9" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国农业信贷银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT AGRICOLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'XIAMEN ITG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -1687,22 +1687,22 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>r119_christiandior</t>
+          <t>r147_aviationindustrycorpofchina</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>迪奥公司</t>
+          <t>中国航空工业集团有限公司</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>CHRISTIAN DIOR</t>
+          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1720,12 +1720,12 @@
       <c r="I16" s="9" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“迪奥公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHRISTIAN DIOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AVIATION INDUSTRY CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -1742,22 +1742,22 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>r122_carrefour</t>
+          <t>r155_energytransfer公司</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>家乐福</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>CARREFOUR</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1775,12 +1775,12 @@
       <c r="I17" s="9" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“家乐福”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CARREFOUR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Energy Transfer公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -1797,22 +1797,22 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>r129_chinafawgroup</t>
+          <t>r160_chinanorthindustriesgroup</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>中国第一汽车集团有限公司</t>
+          <t>中国兵器工业集团有限公司</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>CHINA FAW GROUP</t>
+          <t>CHINA NORTH INDUSTRIES GROUP</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1830,12 +1830,12 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国第一汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA FAW GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NORTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -1852,22 +1852,22 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>r138_zhejiangrongshengholdinggroup</t>
+          <t>r161_pacificconstructiongroup</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>浙江荣盛控股集团有限公司</t>
+          <t>太平洋建设集团有限公司</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
+          <t>PACIFIC CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1885,12 +1885,12 @@
       <c r="I19" s="9" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG RONGSHENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PACIFIC CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -1907,22 +1907,22 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>r142_xiamenitgholdinggroup</t>
+          <t>r167_petronas</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>厦门国贸控股集团有限公司</t>
+          <t>马来西亚国家石油公司</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>XIAMEN ITG HOLDING GROUP</t>
+          <t>PETRONAS</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1940,12 +1940,12 @@
       <c r="I20" s="9" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“马来西亚国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'XIAMEN ITG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PETRONAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -1962,22 +1962,22 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>r147_aviationindustrycorpofchina</t>
+          <t>r171_shenghongholdinggroup</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>中国航空工业集团有限公司</t>
+          <t>盛虹控股集团有限公司</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
+          <t>SHENGHONG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1995,12 +1995,12 @@
       <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“盛虹控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AVIATION INDUSTRY CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHENGHONG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -2017,22 +2017,22 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>r155_energytransfer公司</t>
+          <t>r172_basf</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>172</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>巴斯夫公司</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2050,12 +2050,12 @@
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴斯夫公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Energy Transfer公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BASF'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2072,22 +2072,22 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>r160_chinanorthindustriesgroup</t>
+          <t>r175_shandongweiqiaopioneeringgroup</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司</t>
+          <t>山东魏桥创业集团有限公司</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>CHINA NORTH INDUSTRIES GROUP</t>
+          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2105,12 +2105,12 @@
       <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NORTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG WEIQIAO PIONEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -2127,22 +2127,22 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>r161_pacificconstructiongroup</t>
+          <t>r180_oilandnaturalgas</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>太平洋建设集团有限公司</t>
+          <t>印度石油天然气公司</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>PACIFIC CONSTRUCTION GROUP</t>
+          <t>OIL &amp; NATURAL GAS</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2160,12 +2160,12 @@
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“印度石油天然气公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PACIFIC CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'OIL &amp; NATURAL GAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -2182,22 +2182,22 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>r167_petronas</t>
+          <t>r187_xmxyg</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>马来西亚国家石油公司</t>
+          <t>厦门象屿集团有限公司</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>PETRONAS</t>
+          <t>XMXYG</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2215,12 +2215,12 @@
       <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“马来西亚国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“厦门象屿集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PETRONAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'XMXYG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -2237,22 +2237,22 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>r171_shenghongholdinggroup</t>
+          <t>r188_rtx</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>盛虹控股集团有限公司</t>
+          <t>雷神技术公司</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>SHENGHONG HOLDING GROUP</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2270,12 +2270,12 @@
       <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“盛虹控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“雷神技术公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHENGHONG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'RTX'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -2292,22 +2292,22 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>r172_basf</t>
+          <t>r194_koc集团</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>巴斯夫公司</t>
+          <t>KOC集团</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>KOC集团</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2325,12 +2325,12 @@
       <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴斯夫公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“KOC集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BASF'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KOC集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -2347,22 +2347,22 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>r175_shandongweiqiaopioneeringgroup</t>
+          <t>r210_unilever</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>山东魏桥创业集团有限公司</t>
+          <t>联合利华</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
+          <t>UNILEVER</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2380,12 +2380,12 @@
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“联合利华”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG WEIQIAO PIONEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'UNILEVER'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -2402,22 +2402,22 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>r178_statebankofindia</t>
+          <t>r213_jinnengholdinggroup</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>印度国家银行</t>
+          <t>晋能控股集团有限公司</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>STATE BANK OF INDIA</t>
+          <t>JINNENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2435,12 +2435,12 @@
       <c r="I29" s="9" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度国家银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“晋能控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE BANK OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINNENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -2457,22 +2457,22 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>r180_oilandnaturalgas</t>
+          <t>r216_sberbank</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>印度石油天然气公司</t>
+          <t>俄罗斯联邦储蓄银行</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>OIL &amp; NATURAL GAS</t>
+          <t>SBERBANK</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2490,12 +2490,12 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度石油天然气公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯联邦储蓄银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'OIL &amp; NATURAL GAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SBERBANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
@@ -2512,22 +2512,22 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>r187_xmxyg</t>
+          <t>r218_progressive</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>厦门象屿集团有限公司</t>
+          <t>前进保险公司</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>XMXYG</t>
+          <t>PROGRESSIVE</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2545,12 +2545,12 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“厦门象屿集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“前进保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'XMXYG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PROGRESSIVE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
@@ -2567,22 +2567,22 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>r188_rtx</t>
+          <t>r219_internationalbusinessmachines</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>雷神技术公司</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>INTERNATIONAL BUSINESS MACHINES</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2600,12 +2600,12 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“雷神技术公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国际商业机器公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'RTX'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'INTERNATIONAL BUSINESS MACHINES'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -2622,22 +2622,22 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>r194_koc集团</t>
+          <t>r229_merck</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>KOC集团</t>
+          <t>默沙东</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>KOC集团</t>
+          <t>MERCK</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2655,12 +2655,12 @@
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“KOC集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“默沙东”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KOC集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MERCK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -2677,22 +2677,22 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>r197_rochegroup</t>
+          <t>r232_industrialbank</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>瑞士罗氏公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>ROCHE GROUP</t>
+          <t>INDUSTRIAL BANK</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2710,12 +2710,12 @@
       <c r="I34" s="9" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“瑞士罗氏公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“兴业银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ROCHE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'INDUSTRIAL BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -2732,22 +2732,22 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>r200_bancobilbaovizcayaargentaria</t>
+          <t>r233_poscoholdings</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>西班牙对外银行</t>
+          <t>浦项制铁控股公司</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
+          <t>POSCO HOLDINGS</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2765,12 +2765,12 @@
       <c r="I35" s="9" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“西班牙对外银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浦项制铁控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANCO BILBAO VIZCAYA ARGENTARIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'POSCO HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -2787,22 +2787,22 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>r204_lloydsbankinggroup</t>
+          <t>r238_chinahuanenggroup</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>英国劳埃德银行集团</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>LLOYDS BANKING GROUP</t>
+          <t>CHINA HUANENG GROUP</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2820,12 +2820,12 @@
       <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“英国劳埃德银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国华能集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LLOYDS BANKING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUANENG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
@@ -2842,22 +2842,22 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>r205_deutschebank</t>
+          <t>r239_chinaenergyengineeringgroup</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>德意志银行</t>
+          <t>中国能源建设集团有限公司</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK</t>
+          <t>CHINA ENERGY ENGINEERING GROUP</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2875,12 +2875,12 @@
       <c r="I37" s="9" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德意志银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国能源建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DEUTSCHE BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ENERGY ENGINEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -2897,22 +2897,22 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>r210_unilever</t>
+          <t>r240_dongfengmotor</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>联合利华</t>
+          <t>东风汽车集团有限公司</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>UNILEVER</t>
+          <t>DONGFENG MOTOR</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2930,12 +2930,12 @@
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“联合利华”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“东风汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'UNILEVER'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DONGFENG MOTOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -2952,22 +2952,22 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>r213_jinnengholdinggroup</t>
+          <t>r242_publixsupermarkets</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>晋能控股集团有限公司</t>
+          <t>大众超级市场公司</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>JINNENG HOLDING GROUP</t>
+          <t>PUBLIX SUPER MARKETS</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2985,12 +2985,12 @@
       <c r="I39" s="9" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“晋能控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“大众超级市场公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINNENG HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PUBLIX SUPER MARKETS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3007,22 +3007,22 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>r214_aluminumcorpofchina</t>
+          <t>r243_zhejianghengyigroup</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司</t>
+          <t>浙江恒逸集团有限公司</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>ALUMINUM CORP. OF CHINA</t>
+          <t>ZHEJIANG HENGYI GROUP</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3040,12 +3040,12 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国铝业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江恒逸集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ALUMINUM CORP. OF CHINA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG HENGYI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -3062,22 +3062,22 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>r216_sberbank</t>
+          <t>r245_assicurazionigenerali</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>俄罗斯联邦储蓄银行</t>
+          <t>意大利忠利保险公司</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>SBERBANK</t>
+          <t>ASSICURAZIONI GENERALI</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3095,12 +3095,12 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“俄罗斯联邦储蓄银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“意大利忠利保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SBERBANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ASSICURAZIONI GENERALI'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -3117,22 +3117,22 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>r218_progressive</t>
+          <t>r249_hbisgroup</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>249</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>前进保险公司</t>
+          <t>河钢集团有限公司</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>PROGRESSIVE</t>
+          <t>HBIS GROUP</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3150,12 +3150,12 @@
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“前进保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“河钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PROGRESSIVE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HBIS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
@@ -3172,22 +3172,22 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>r219_internationalbusinessmachines</t>
+          <t>r253_chinaelectronicstechnologygroup</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>国际商业机器公司</t>
+          <t>中国电子科技集团有限公司</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>INTERNATIONAL BUSINESS MACHINES</t>
+          <t>CHINA ELECTRONICS TECHNOLOGY GROUP</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3205,12 +3205,12 @@
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“国际商业机器公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国电子科技集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'INTERNATIONAL BUSINESS MACHINES'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS TECHNOLOGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
@@ -3227,22 +3227,22 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>r229_merck</t>
+          <t>r254_nationwide</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>254</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>默沙东</t>
+          <t>美国全国保险公司</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>MERCK</t>
+          <t>NATIONWIDE</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3260,12 +3260,12 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“默沙东”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国全国保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MERCK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NATIONWIDE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -3282,22 +3282,22 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>r232_industrialbank</t>
+          <t>r256_statepowerinvestment</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>国家电力投资集团有限公司</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>INDUSTRIAL BANK</t>
+          <t>STATE POWER INVESTMENT</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3315,12 +3315,12 @@
       <c r="I45" s="9" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“兴业银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国家电力投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'INDUSTRIAL BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'STATE POWER INVESTMENT'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -3337,22 +3337,22 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>r233_poscoholdings</t>
+          <t>r265_tsingshanholdinggroup</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>浦项制铁控股公司</t>
+          <t>青山控股集团有限公司</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>POSCO HOLDINGS</t>
+          <t>TSINGSHAN HOLDING GROUP</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3370,12 +3370,12 @@
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浦项制铁控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“青山控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'POSCO HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TSINGSHAN HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>r238_chinahuanenggroup</t>
+          <t>r267_coscoshipping</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司</t>
+          <t>中国远洋海运集团有限公司</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>CHINA HUANENG GROUP</t>
+          <t>COSCO SHIPPING</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -3425,12 +3425,12 @@
       <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国华能集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国远洋海运集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUANENG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COSCO SHIPPING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>r239_chinaenergyengineeringgroup</t>
+          <t>r274_deutschebahn</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>274</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>中国能源建设集团有限公司</t>
+          <t>德国联邦铁路公司</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>CHINA ENERGY ENGINEERING GROUP</t>
+          <t>DEUTSCHE BAHN</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -3480,12 +3480,12 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国能源建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国联邦铁路公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ENERGY ENGINEERING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DEUTSCHE BAHN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -3502,22 +3502,22 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>r024_glencore</t>
+          <t>r276_tysonfoods</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>嘉能可</t>
+          <t>泰森食品</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>GLENCORE</t>
+          <t>TYSON FOODS</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -3535,12 +3535,12 @@
       <c r="I49" s="9" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“嘉能可”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“泰森食品”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GLENCORE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TYSON FOODS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
@@ -3557,22 +3557,22 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>r240_dongfengmotor</t>
+          <t>r277_mideagroup</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>东风汽车集团有限公司</t>
+          <t>美的集团股份有限公司</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>DONGFENG MOTOR</t>
+          <t>MIDEA GROUP</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -3590,12 +3590,12 @@
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“东风汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美的集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DONGFENG MOTOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MIDEA GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
@@ -3612,22 +3612,22 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>r242_publixsupermarkets</t>
+          <t>r279_chinaunitednetworkcommunications</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>大众超级市场公司</t>
+          <t>中国联合网络通信股份有限公司</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>PUBLIX SUPER MARKETS</t>
+          <t>CHINA UNITED NETWORK COMMUNICATIONS</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -3645,12 +3645,12 @@
       <c r="I51" s="9" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“大众超级市场公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国联合网络通信股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PUBLIX SUPER MARKETS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA UNITED NETWORK COMMUNICATIONS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
@@ -3667,22 +3667,22 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>r243_zhejianghengyigroup</t>
+          <t>r280_libertymutualinsurancegroup</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>浙江恒逸集团有限公司</t>
+          <t>美国利宝互助保险集团</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>ZHEJIANG HENGYI GROUP</t>
+          <t>LIBERTY MUTUAL INSURANCE GROUP</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -3700,12 +3700,12 @@
       <c r="I52" s="9" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江恒逸集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国利宝互助保险集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG HENGYI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LIBERTY MUTUAL INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
@@ -3722,22 +3722,22 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>r245_assicurazionigenerali</t>
+          <t>r281_bankofnovascotia</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>意大利忠利保险公司</t>
+          <t>加拿大丰业银行</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI</t>
+          <t>BANK OF NOVA SCOTIA</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3755,12 +3755,12 @@
       <c r="I53" s="9" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“意大利忠利保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大丰业银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ASSICURAZIONI GENERALI'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF NOVA SCOTIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -3777,22 +3777,22 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>r249_hbisgroup</t>
+          <t>r284_saintgobain</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>河钢集团有限公司</t>
+          <t>圣戈班集团</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>HBIS GROUP</t>
+          <t>SAINT-GOBAIN</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3810,12 +3810,12 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“河钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“圣戈班集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HBIS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SAINT-GOBAIN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
@@ -3832,22 +3832,22 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>r253_chinaelectronicstechnologygroup</t>
+          <t>r285_shaanxiyanchangpetroleumgroup</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>中国电子科技集团有限公司</t>
+          <t>陕西延长石油（集团）有限责任公司</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>CHINA ELECTRONICS TECHNOLOGY GROUP</t>
+          <t>SHAANXI YANCHANG PETROLEUM (GROUP)</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3865,12 +3865,12 @@
       <c r="I55" s="9" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国电子科技集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“陕西延长石油（集团）有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS TECHNOLOGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI YANCHANG PETROLEUM (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -3887,22 +3887,22 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>r254_nationwide</t>
+          <t>r288_nike</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>美国全国保险公司</t>
+          <t>耐克公司</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>NATIONWIDE</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3920,12 +3920,12 @@
       <c r="I56" s="9" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国全国保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“耐克公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NATIONWIDE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NIKE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
@@ -3942,22 +3942,22 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>r256_statepowerinvestment</t>
+          <t>r291_greenlandholdinggroup</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>国家电力投资集团有限公司</t>
+          <t>绿地控股集团股份有限公司</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>STATE POWER INVESTMENT</t>
+          <t>GREENLAND HOLDING GROUP</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3975,12 +3975,12 @@
       <c r="I57" s="9" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“国家电力投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“绿地控股集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE POWER INVESTMENT'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GREENLAND HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
@@ -3997,22 +3997,22 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>r265_tsingshanholdinggroup</t>
+          <t>r292_shanghaipudongdevelopmentbank</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>292</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>青山控股集团有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>TSINGSHAN HOLDING GROUP</t>
+          <t>SHANGHAI PUDONG DEVELOPMENT BANK</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“青山控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海浦东发展银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TSINGSHAN HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PUDONG DEVELOPMENT BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
@@ -4052,22 +4052,22 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>r267_coscoshipping</t>
+          <t>r293_louisdreyfus</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>293</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司</t>
+          <t>路易达孚集团</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>COSCO SHIPPING</t>
+          <t>LOUIS DREYFUS</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -4085,12 +4085,12 @@
       <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国远洋海运集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“路易达孚集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COSCO SHIPPING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LOUIS DREYFUS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
@@ -4107,22 +4107,22 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>r274_deutschebahn</t>
+          <t>r296_kb金融集团</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>德国联邦铁路公司</t>
+          <t>KB金融集团</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>DEUTSCHE BAHN</t>
+          <t>KB金融集团</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -4140,12 +4140,12 @@
       <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德国联邦铁路公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“KB金融集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DEUTSCHE BAHN'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KB金融集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
@@ -4162,22 +4162,22 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>r276_tysonfoods</t>
+          <t>r299_oracle</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>泰森食品</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>TYSON FOODS</t>
+          <t>ORACLE</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -4195,12 +4195,12 @@
       <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“泰森食品”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“甲骨文公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TYSON FOODS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ORACLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -4217,22 +4217,22 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>r277_mideagroup</t>
+          <t>r003_stategrid</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>美的集团股份有限公司</t>
+          <t>国家电网有限公司</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>MIDEA GROUP</t>
+          <t>STATE GRID</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -4250,12 +4250,12 @@
       <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美的集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国家电网有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MIDEA GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'STATE GRID'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
@@ -4272,22 +4272,22 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>r279_chinaunitednetworkcommunications</t>
+          <t>r300_jinchuangroup</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>中国联合网络通信股份有限公司</t>
+          <t>金川集团股份有限公司</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>CHINA UNITED NETWORK COMMUNICATIONS</t>
+          <t>JINCHUAN GROUP</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -4305,12 +4305,12 @@
       <c r="I63" s="9" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国联合网络通信股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“金川集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA UNITED NETWORK COMMUNICATIONS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINCHUAN GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr">
@@ -4327,22 +4327,22 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>r280_libertymutualinsurancegroup</t>
+          <t>r303_enterpriseproductspartners公司</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>美国利宝互助保险集团</t>
+          <t>Enterprise Products Partners公司</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>LIBERTY MUTUAL INSURANCE GROUP</t>
+          <t>Enterprise Products Partners公司</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -4360,12 +4360,12 @@
       <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国利宝互助保险集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enterprise Products Partners公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LIBERTY MUTUAL INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enterprise Products Partners公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr">
@@ -4382,22 +4382,22 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>r281_bankofnovascotia</t>
+          <t>r304_capitalonefinancial</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>加拿大丰业银行</t>
+          <t>第一资本金融公司</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>BANK OF NOVA SCOTIA</t>
+          <t>CAPITAL ONE FINANCIAL</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -4415,12 +4415,12 @@
       <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“加拿大丰业银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“第一资本金融公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF NOVA SCOTIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CAPITAL ONE FINANCIAL'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
@@ -4437,22 +4437,22 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>r284_saintgobain</t>
+          <t>r306_hdfc银行</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>圣戈班集团</t>
+          <t>HDFC银行</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>SAINT-GOBAIN</t>
+          <t>HDFC银行</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -4470,12 +4470,12 @@
       <c r="I66" s="9" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“圣戈班集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“HDFC银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SAINT-GOBAIN'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HDFC银行'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr">
@@ -4492,22 +4492,22 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>r285_shaanxiyanchangpetroleumgroup</t>
+          <t>r307_chinanationalbuildingmaterialgroup</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>陕西延长石油（集团）有限责任公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>SHAANXI YANCHANG PETROLEUM (GROUP)</t>
+          <t>CHINA NATIONAL BUILDING MATERIAL GROUP</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -4525,12 +4525,12 @@
       <c r="I67" s="9" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“陕西延长石油（集团）有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国建材集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI YANCHANG PETROLEUM (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL BUILDING MATERIAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L67" s="9" t="inlineStr">
@@ -4547,22 +4547,22 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>r288_nike</t>
+          <t>r309_chinastateshipbuilding</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>耐克公司</t>
+          <t>中国船舶集团有限公司</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>CHINA STATE SHIPBUILDING</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -4580,12 +4580,12 @@
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“耐克公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国船舶集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NIKE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA STATE SHIPBUILDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
@@ -4602,22 +4602,22 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>r291_greenlandholdinggroup</t>
+          <t>r312_landesbankbadenwürttemberg</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>绿地控股集团股份有限公司</t>
+          <t>德国巴登-符腾堡州银行</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>GREENLAND HOLDING GROUP</t>
+          <t>LANDESBANK BADEN-WÜRTTEMBERG</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -4635,12 +4635,12 @@
       <c r="I69" s="9" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“绿地控股集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国巴登-符腾堡州银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GREENLAND HOLDING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LANDESBANK BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
@@ -4657,22 +4657,22 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>r292_shanghaipudongdevelopmentbank</t>
+          <t>r314_jingyegroup</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>敬业集团有限公司</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI PUDONG DEVELOPMENT BANK</t>
+          <t>JINGYE GROUP</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -4690,12 +4690,12 @@
       <c r="I70" s="9" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海浦东发展银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“敬业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PUDONG DEVELOPMENT BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JINGYE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr">
@@ -4712,22 +4712,22 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>r293_louisdreyfus</t>
+          <t>r316_energiebadenwürttemberg</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>路易达孚集团</t>
+          <t>巴登-符腾堡州能源公司</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>LOUIS DREYFUS</t>
+          <t>ENERGIE BADEN-WÜRTTEMBERG</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -4745,12 +4745,12 @@
       <c r="I71" s="9" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“路易达孚集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴登-符腾堡州能源公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LOUIS DREYFUS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ENERGIE BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L71" s="9" t="inlineStr">
@@ -4767,22 +4767,22 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>r296_kb金融集团</t>
+          <t>r321_hd现代公司</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>KB金融集团</t>
+          <t>HD现代公司</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>KB金融集团</t>
+          <t>HD现代公司</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -4800,12 +4800,12 @@
       <c r="I72" s="9" t="inlineStr"/>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“KB金融集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“HD现代公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KB金融集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HD现代公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
@@ -4822,22 +4822,22 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>r299_oracle</t>
+          <t>r325_softbankgroup</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>325</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>软银集团</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>ORACLE</t>
+          <t>SOFTBANK GROUP</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -4855,12 +4855,12 @@
       <c r="I73" s="9" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“甲骨文公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“软银集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ORACLE'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SOFTBANK GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
@@ -4877,22 +4877,22 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>r003_stategrid</t>
+          <t>r328_américamóvil</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>国家电网有限公司</t>
+          <t>美洲电信</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>STATE GRID</t>
+          <t>AMÉRICA MÓVIL</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -4910,12 +4910,12 @@
       <c r="I74" s="9" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“国家电网有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美洲电信”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE GRID'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AMÉRICA MÓVIL'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
@@ -4932,22 +4932,22 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>r300_jinchuangroup</t>
+          <t>r330_zhejiangcommunicationsinvestmentgroup</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司</t>
+          <t>浙江省交通投资集团有限公司</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>JINCHUAN GROUP</t>
+          <t>ZHEJIANG COMMUNICATIONS INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -4965,12 +4965,12 @@
       <c r="I75" s="9" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“金川集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江省交通投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINCHUAN GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG COMMUNICATIONS INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
@@ -4987,22 +4987,22 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>r303_enterpriseproductspartners公司</t>
+          <t>r331_chinapacificinsurancegroup</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners公司</t>
+          <t>中国太平洋保险(集团)股份有限公司</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners公司</t>
+          <t>CHINA PACIFIC INSURANCE (GROUP)</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -5020,12 +5020,12 @@
       <c r="I76" s="9" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enterprise Products Partners公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国太平洋保险(集团)股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enterprise Products Partners公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA PACIFIC INSURANCE (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr">
@@ -5042,22 +5042,22 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>r304_capitalonefinancial</t>
+          <t>r332_cocacola</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>332</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>第一资本金融公司</t>
+          <t>可口可乐公司</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>CAPITAL ONE FINANCIAL</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -5075,12 +5075,12 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“第一资本金融公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“可口可乐公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CAPITAL ONE FINANCIAL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COCA-COLA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
@@ -5097,22 +5097,22 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>r306_hdfc银行</t>
+          <t>r336_chinahuadian</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>HDFC银行</t>
+          <t>中国华电集团有限公司</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>HDFC银行</t>
+          <t>CHINA HUADIAN</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -5130,12 +5130,12 @@
       <c r="I78" s="9" t="inlineStr"/>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“HDFC银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国华电集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HDFC银行'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUADIAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
@@ -5152,22 +5152,22 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>r307_chinanationalbuildingmaterialgroup</t>
+          <t>r337_créditmutuelgroup</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>法国国民互助信贷银行集团</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL BUILDING MATERIAL GROUP</t>
+          <t>CRÉDIT MUTUEL GROUP</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -5185,12 +5185,12 @@
       <c r="I79" s="9" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国建材集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国国民互助信贷银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL BUILDING MATERIAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT MUTUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
@@ -5207,22 +5207,22 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>r309_chinastateshipbuilding</t>
+          <t>r338_msandad保险集团控股有限公司</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>中国船舶集团有限公司</t>
+          <t>MS&amp;AD保险集团控股有限公司</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>CHINA STATE SHIPBUILDING</t>
+          <t>MS&amp;AD保险集团控股有限公司</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -5240,12 +5240,12 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国船舶集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“MS&amp;AD保险集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA STATE SHIPBUILDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MS&amp;AD保险集团控股有限公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
@@ -5262,22 +5262,22 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>r312_landesbankbadenwürttemberg</t>
+          <t>r340_susunconstructiongroup</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>340</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>德国巴登-符腾堡州银行</t>
+          <t>苏商建设集团有限公司</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>LANDESBANK BADEN-WÜRTTEMBERG</t>
+          <t>SUSUN CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -5295,12 +5295,12 @@
       <c r="I81" s="9" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德国巴登-符腾堡州银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“苏商建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LANDESBANK BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SUSUN CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
@@ -5317,22 +5317,22 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>r314_jingyegroup</t>
+          <t>r341_sncfgroup</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>敬业集团有限公司</t>
+          <t>法国国营铁路集团</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>JINGYE GROUP</t>
+          <t>SNCF GROUP</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -5350,12 +5350,12 @@
       <c r="I82" s="9" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“敬业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国国营铁路集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JINGYE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SNCF GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L82" s="9" t="inlineStr">
@@ -5372,22 +5372,22 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>r316_energiebadenwürttemberg</t>
+          <t>r343_chinasouthindustriesgroup</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>343</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>巴登-符腾堡州能源公司</t>
+          <t>中国兵器装备集团公司</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>ENERGIE BADEN-WÜRTTEMBERG</t>
+          <t>CHINA SOUTH INDUSTRIES GROUP</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -5405,12 +5405,12 @@
       <c r="I83" s="9" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴登-符腾堡州能源公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国兵器装备集团公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ENERGIE BADEN-WÜRTTEMBERG'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA SOUTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
@@ -5427,22 +5427,22 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>r321_hd现代公司</t>
+          <t>r347_georgeweston</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>HD现代公司</t>
+          <t>乔治威斯顿公司</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>HD现代公司</t>
+          <t>GEORGE WESTON</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -5460,12 +5460,12 @@
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“HD现代公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“乔治威斯顿公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HD现代公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GEORGE WESTON'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L84" s="9" t="inlineStr">
@@ -5482,22 +5482,22 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>r325_softbankgroup</t>
+          <t>r351_chinaminshengbanking</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>软银集团</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>SOFTBANK GROUP</t>
+          <t>CHINA MINSHENG BANKING</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -5515,12 +5515,12 @@
       <c r="I85" s="9" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“软银集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国民生银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SOFTBANK GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA MINSHENG BANKING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L85" s="9" t="inlineStr">
@@ -5537,22 +5537,22 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>r328_américamóvil</t>
+          <t>r354_shanghaiconstructiongroup</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>美洲电信</t>
+          <t>上海建工集团股份有限公司</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>AMÉRICA MÓVIL</t>
+          <t>SHANGHAI CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -5570,12 +5570,12 @@
       <c r="I86" s="9" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美洲电信”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海建工集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AMÉRICA MÓVIL'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr">
@@ -5592,22 +5592,22 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>r330_zhejiangcommunicationsinvestmentgroup</t>
+          <t>r355_lg化学公司</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司</t>
+          <t>LG化学公司</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>ZHEJIANG COMMUNICATIONS INVESTMENT GROUP</t>
+          <t>LG化学公司</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -5625,12 +5625,12 @@
       <c r="I87" s="9" t="inlineStr"/>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江省交通投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“LG化学公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZHEJIANG COMMUNICATIONS INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LG化学公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L87" s="9" t="inlineStr">
@@ -5647,22 +5647,22 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>r331_chinapacificinsurancegroup</t>
+          <t>r360_unitedservicesautomobileassn</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>中国太平洋保险(集团)股份有限公司</t>
+          <t>联合服务汽车协会</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>CHINA PACIFIC INSURANCE (GROUP)</t>
+          <t>UNITED SERVICES AUTOMOBILE ASSN.</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -5680,12 +5680,12 @@
       <c r="I88" s="9" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国太平洋保险(集团)股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“联合服务汽车协会”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA PACIFIC INSURANCE (GROUP)'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'UNITED SERVICES AUTOMOBILE ASSN.'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L88" s="9" t="inlineStr">
@@ -5702,22 +5702,22 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>r332_cocacola</t>
+          <t>r361_guangzhoumunicipalconstructiongroup</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>可口可乐公司</t>
+          <t>广州市建筑集团有限公司</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>GUANGZHOU MUNICIPAL CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -5735,12 +5735,12 @@
       <c r="I89" s="9" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“可口可乐公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州市建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COCA-COLA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU MUNICIPAL CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>r336_chinahuadian</t>
+          <t>r362_generaldynamics</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>中国华电集团有限公司</t>
+          <t>通用动力</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>CHINA HUADIAN</t>
+          <t>GENERAL DYNAMICS</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -5790,12 +5790,12 @@
       <c r="I90" s="9" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国华电集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“通用动力”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA HUADIAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GENERAL DYNAMICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
@@ -5812,22 +5812,22 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>r337_créditmutuelgroup</t>
+          <t>r364_zijinmininggroup</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>法国国民互助信贷银行集团</t>
+          <t>紫金矿业集团股份有限公司</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>CRÉDIT MUTUEL GROUP</t>
+          <t>ZIJIN MINING GROUP</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -5845,12 +5845,12 @@
       <c r="I91" s="9" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国国民互助信贷银行集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“紫金矿业集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CRÉDIT MUTUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ZIJIN MINING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L91" s="9" t="inlineStr">
@@ -5867,22 +5867,22 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>r338_msandad保险集团控股有限公司</t>
+          <t>r370_shenzheninvestmentholdings</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>MS&amp;AD保险集团控股有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>MS&amp;AD保险集团控股有限公司</t>
+          <t>SHENZHEN INVESTMENT HOLDINGS</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -5900,12 +5900,12 @@
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“MS&amp;AD保险集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“深圳市投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MS&amp;AD保险集团控股有限公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHENZHEN INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr">
@@ -5922,22 +5922,22 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>r340_susunconstructiongroup</t>
+          <t>r371_ansteelgroup</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>苏商建设集团有限公司</t>
+          <t>鞍钢集团有限公司</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>SUSUN CONSTRUCTION GROUP</t>
+          <t>ANSTEEL GROUP</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -5955,12 +5955,12 @@
       <c r="I93" s="9" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“苏商建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“鞍钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SUSUN CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'ANSTEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L93" s="9" t="inlineStr">
@@ -5977,22 +5977,22 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>r341_sncfgroup</t>
+          <t>r372_hanwha</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>法国国营铁路集团</t>
+          <t>韩华集团</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>SNCF GROUP</t>
+          <t>HANWHA</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -6010,12 +6010,12 @@
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国国营铁路集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“韩华集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SNCF GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANWHA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L94" s="9" t="inlineStr">
@@ -6032,22 +6032,22 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>r343_chinasouthindustriesgroup</t>
+          <t>r373_usbancorp</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>中国兵器装备集团公司</t>
+          <t>美国合众银行</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>CHINA SOUTH INDUSTRIES GROUP</t>
+          <t>U.S. BANCORP</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -6065,12 +6065,12 @@
       <c r="I95" s="9" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国兵器装备集团公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国合众银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA SOUTH INDUSTRIES GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'U.S. BANCORP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
@@ -6087,22 +6087,22 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>r347_georgeweston</t>
+          <t>r377_thyssenkrupp</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>乔治威斯顿公司</t>
+          <t>蒂森克虏伯</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>GEORGE WESTON</t>
+          <t>THYSSENKRUPP</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -6120,12 +6120,12 @@
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“乔治威斯顿公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“蒂森克虏伯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GEORGE WESTON'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'THYSSENKRUPP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L96" s="9" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>r351_chinaminshengbanking</t>
+          <t>r380_chinanationalnuclear</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中国核工业集团有限公司</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>CHINA MINSHENG BANKING</t>
+          <t>CHINA NATIONAL NUCLEAR</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -6175,12 +6175,12 @@
       <c r="I97" s="9" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国民生银行股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国核工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA MINSHENG BANKING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL NUCLEAR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L97" s="9" t="inlineStr">
@@ -6197,22 +6197,22 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>r354_shanghaiconstructiongroup</t>
+          <t>r381_taikanginsurancegroup</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>上海建工集团股份有限公司</t>
+          <t>泰康保险集团股份有限公司</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI CONSTRUCTION GROUP</t>
+          <t>TAIKANG INSURANCE GROUP</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -6230,12 +6230,12 @@
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海建工集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“泰康保险集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TAIKANG INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr">
@@ -6252,22 +6252,22 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>r355_lg化学公司</t>
+          <t>r382_northropgrumman</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>LG化学公司</t>
+          <t>美国诺斯洛普格拉曼公司</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>LG化学公司</t>
+          <t>NORTHROP GRUMMAN</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -6285,12 +6285,12 @@
       <c r="I99" s="9" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“LG化学公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国诺斯洛普格拉曼公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LG化学公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NORTHROP GRUMMAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
@@ -6307,22 +6307,22 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>r360_unitedservicesautomobileassn</t>
+          <t>r383_jiangsushaganggroup</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>联合服务汽车协会</t>
+          <t>江苏沙钢集团有限公司</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>UNITED SERVICES AUTOMOBILE ASSN.</t>
+          <t>JIANGSU SHAGANG GROUP</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -6340,12 +6340,12 @@
       <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“联合服务汽车协会”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“江苏沙钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'UNITED SERVICES AUTOMOBILE ASSN.'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'JIANGSU SHAGANG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L100" s="9" t="inlineStr">
@@ -6362,22 +6362,22 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>r361_guangzhoumunicipalconstructiongroup</t>
+          <t>r389_dollargeneral公司</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>广州市建筑集团有限公司</t>
+          <t>Dollar General公司</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU MUNICIPAL CONSTRUCTION GROUP</t>
+          <t>Dollar General公司</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -6395,12 +6395,12 @@
       <c r="I101" s="9" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州市建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Dollar General公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU MUNICIPAL CONSTRUCTION GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Dollar General公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L101" s="9" t="inlineStr">
@@ -6417,22 +6417,22 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>r362_generaldynamics</t>
+          <t>r390_cenovusenergy公司</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>通用动力</t>
+          <t>Cenovus Energy公司</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>GENERAL DYNAMICS</t>
+          <t>Cenovus Energy公司</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -6450,12 +6450,12 @@
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“通用动力”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Cenovus Energy公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GENERAL DYNAMICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Cenovus Energy公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L102" s="9" t="inlineStr">
@@ -6472,22 +6472,22 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>r364_zijinmininggroup</t>
+          <t>r393_fairfaxfinancialholdings</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>393</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>紫金矿业集团股份有限公司</t>
+          <t>加拿大枫信金融控股公司</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>ZIJIN MINING GROUP</t>
+          <t>FAIRFAX FINANCIAL HOLDINGS</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -6505,12 +6505,12 @@
       <c r="I103" s="9" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“紫金矿业集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大枫信金融控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ZIJIN MINING GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'FAIRFAX FINANCIAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L103" s="9" t="inlineStr">
@@ -6527,22 +6527,22 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>r370_shenzheninvestmentholdings</t>
+          <t>r394_guangzhouindustrialinvestmentholdings</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>394</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>广州工业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>SHENZHEN INVESTMENT HOLDINGS</t>
+          <t>GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -6560,12 +6560,12 @@
       <c r="I104" s="9" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“深圳市投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州工业投资控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHENZHEN INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L104" s="9" t="inlineStr">
@@ -6582,22 +6582,22 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>r371_ansteelgroup</t>
+          <t>r040_elevancehealth公司</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>鞍钢集团有限公司</t>
+          <t>Elevance Health公司</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>ANSTEEL GROUP</t>
+          <t>Elevance Health公司</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -6615,12 +6615,12 @@
       <c r="I105" s="9" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“鞍钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Elevance Health公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'ANSTEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Elevance Health公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L105" s="9" t="inlineStr">
@@ -6637,22 +6637,22 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>r372_hanwha</t>
+          <t>r402_hangzhouindustrialinvestmentgroup</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>402</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>韩华集团</t>
+          <t>杭州市实业投资集团有限公司</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>HANWHA</t>
+          <t>HANGZHOU INDUSTRIAL INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -6670,12 +6670,12 @@
       <c r="I106" s="9" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“韩华集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“杭州市实业投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANWHA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU INDUSTRIAL INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr">
@@ -6692,22 +6692,22 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>r373_usbancorp</t>
+          <t>r404_dzbank</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>美国合众银行</t>
+          <t>德国中央合作银行</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>U.S. BANCORP</t>
+          <t>DZ BANK</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -6725,12 +6725,12 @@
       <c r="I107" s="9" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国合众银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“德国中央合作银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'U.S. BANCORP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'DZ BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L107" s="9" t="inlineStr">
@@ -6747,22 +6747,22 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>r377_thyssenkrupp</t>
+          <t>r405_gs加德士</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>405</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>蒂森克虏伯</t>
+          <t>GS加德士</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP</t>
+          <t>GS加德士</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -6780,12 +6780,12 @@
       <c r="I108" s="9" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“蒂森克虏伯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“GS加德士”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'THYSSENKRUPP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GS加德士'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L108" s="9" t="inlineStr">
@@ -6802,22 +6802,22 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>r038_bankofamerica</t>
+          <t>r408_x5零售集团</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>408</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>美国银行</t>
+          <t>X5零售集团</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>BANK OF AMERICA</t>
+          <t>X5零售集团</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -6835,12 +6835,12 @@
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“X5零售集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BANK OF AMERICA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'X5零售集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr">
@@ -6857,22 +6857,22 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>r380_chinanationalnuclear</t>
+          <t>r410_hangzhouironandsteelgroup</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>410</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>中国核工业集团有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL NUCLEAR</t>
+          <t>HANGZHOU IRON AND STEEL GROUP</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -6890,12 +6890,12 @@
       <c r="I110" s="9" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国核工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“杭州钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL NUCLEAR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU IRON AND STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L110" s="9" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>r381_taikanginsurancegroup</t>
+          <t>r411_shanghaipharmaceuticalsholding</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>411</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>泰康保险集团股份有限公司</t>
+          <t>上海医药集团股份有限公司</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>TAIKANG INSURANCE GROUP</t>
+          <t>SHANGHAI PHARMACEUTICALS HOLDING</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -6945,12 +6945,12 @@
       <c r="I111" s="9" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“泰康保险集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海医药集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TAIKANG INSURANCE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PHARMACEUTICALS HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L111" s="9" t="inlineStr">
@@ -6967,22 +6967,22 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>r382_northropgrumman</t>
+          <t>r412_shandonghispeedgroup</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>412</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>美国诺斯洛普格拉曼公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>NORTHROP GRUMMAN</t>
+          <t>SHANDONG HI-SPEED GROUP</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -7000,12 +7000,12 @@
       <c r="I112" s="9" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国诺斯洛普格拉曼公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东高速集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NORTHROP GRUMMAN'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG HI-SPEED GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L112" s="9" t="inlineStr">
@@ -7022,22 +7022,22 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>r383_jiangsushaganggroup</t>
+          <t>r414_guangdongguangxinholdingsgroup</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>414</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>江苏沙钢集团有限公司</t>
+          <t>广东省广新控股集团有限公司</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>JIANGSU SHAGANG GROUP</t>
+          <t>GUANGDONG GUANGXIN HOLDINGS GROUP</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -7055,12 +7055,12 @@
       <c r="I113" s="9" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“江苏沙钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广东省广新控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'JIANGSU SHAGANG GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGDONG GUANGXIN HOLDINGS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L113" s="9" t="inlineStr">
@@ -7077,22 +7077,22 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>r389_dollargeneral公司</t>
+          <t>r417_guangzhoupharmaceuticalholdings</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>417</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Dollar General公司</t>
+          <t>广州医药集团有限公司</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Dollar General公司</t>
+          <t>GUANGZHOU PHARMACEUTICAL HOLDINGS</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -7110,12 +7110,12 @@
       <c r="I114" s="9" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Dollar General公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广州医药集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Dollar General公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU PHARMACEUTICAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L114" s="9" t="inlineStr">
@@ -7132,22 +7132,22 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>r390_cenovusenergy公司</t>
+          <t>r419_mapfregroup</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>419</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Cenovus Energy公司</t>
+          <t>曼福集团</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Cenovus Energy公司</t>
+          <t>MAPFRE GROUP</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -7165,12 +7165,12 @@
       <c r="I115" s="9" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Cenovus Energy公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“曼福集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Cenovus Energy公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'MAPFRE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L115" s="9" t="inlineStr">
@@ -7187,22 +7187,22 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>r393_fairfaxfinancialholdings</t>
+          <t>r420_cfe公司</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>420</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>加拿大枫信金融控股公司</t>
+          <t>CFE公司</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>FAIRFAX FINANCIAL HOLDINGS</t>
+          <t>CFE公司</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -7220,12 +7220,12 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“加拿大枫信金融控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“CFE公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FAIRFAX FINANCIAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CFE公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L116" s="9" t="inlineStr">
@@ -7242,22 +7242,22 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>r394_guangzhouindustrialinvestmentholdings</t>
+          <t>r043_chinarailwayconstruction</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>广州工业投资控股集团有限公司</t>
+          <t>中国铁道建筑集团有限公司</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS</t>
+          <t>CHINA RAILWAY CONSTRUCTION</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -7275,12 +7275,12 @@
       <c r="I117" s="9" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州工业投资控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国铁道建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU INDUSTRIAL INVESTMENT HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA RAILWAY CONSTRUCTION'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L117" s="9" t="inlineStr">
@@ -7297,22 +7297,22 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>r040_elevancehealth公司</t>
+          <t>r430_usfoodsholding公司</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>430</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Elevance Health公司</t>
+          <t>US Foods Holding公司</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Elevance Health公司</t>
+          <t>US Foods Holding公司</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -7330,12 +7330,12 @@
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Elevance Health公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“US Foods Holding公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Elevance Health公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'US Foods Holding公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L118" s="9" t="inlineStr">
@@ -7352,22 +7352,22 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>r402_hangzhouindustrialinvestmentgroup</t>
+          <t>r432_migros集团</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>432</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>杭州市实业投资集团有限公司</t>
+          <t>Migros集团</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>HANGZHOU INDUSTRIAL INVESTMENT GROUP</t>
+          <t>Migros集团</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -7385,12 +7385,12 @@
       <c r="I119" s="9" t="inlineStr"/>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“杭州市实业投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Migros集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU INDUSTRIAL INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Migros集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L119" s="9" t="inlineStr">
@@ -7407,22 +7407,22 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>r404_dzbank</t>
+          <t>r435_chinaelectronics</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>435</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>德国中央合作银行</t>
+          <t>中国电子信息产业集团有限公司</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>DZ BANK</t>
+          <t>CHINA ELECTRONICS</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -7440,12 +7440,12 @@
       <c r="I120" s="9" t="inlineStr"/>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“德国中央合作银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国电子信息产业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'DZ BANK'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L120" s="9" t="inlineStr">
@@ -7462,22 +7462,22 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>r405_gs加德士</t>
+          <t>r436_shudaoinvestmentgroup</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>436</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>GS加德士</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>GS加德士</t>
+          <t>SHUDAO INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -7495,12 +7495,12 @@
       <c r="I121" s="9" t="inlineStr"/>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“GS加德士”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“蜀道投资集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GS加德士'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHUDAO INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L121" s="9" t="inlineStr">
@@ -7517,22 +7517,22 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>r408_x5零售集团</t>
+          <t>r437_chinanationalcoalgroup</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>437</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>X5零售集团</t>
+          <t>中国中煤能源集团有限公司</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>X5零售集团</t>
+          <t>CHINA NATIONAL COAL GROUP</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -7550,12 +7550,12 @@
       <c r="I122" s="9" t="inlineStr"/>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“X5零售集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国中煤能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'X5零售集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L122" s="9" t="inlineStr">
@@ -7572,22 +7572,22 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>r410_hangzhouironandsteelgroup</t>
+          <t>r438_tonglingnonferrousmetalsgroup</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>铜陵有色金属集团控股有限公司</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>HANGZHOU IRON AND STEEL GROUP</t>
+          <t>TONGLING NONFERROUS METALS GROUP</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -7605,12 +7605,12 @@
       <c r="I123" s="9" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“杭州钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“铜陵有色金属集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HANGZHOU IRON AND STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'TONGLING NONFERROUS METALS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L123" s="9" t="inlineStr">
@@ -7627,22 +7627,22 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>r411_shanghaipharmaceuticalsholding</t>
+          <t>r439_ckhutchisonholdings</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>439</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>上海医药集团股份有限公司</t>
+          <t>长江和记实业有限公司</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI PHARMACEUTICALS HOLDING</t>
+          <t>CK HUTCHISON HOLDINGS</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -7660,12 +7660,12 @@
       <c r="I124" s="9" t="inlineStr"/>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海医药集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“长江和记实业有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI PHARMACEUTICALS HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CK HUTCHISON HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L124" s="9" t="inlineStr">
@@ -7682,22 +7682,22 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>r412_shandonghispeedgroup</t>
+          <t>r442_pddholdings</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>442</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>拼多多控股公司</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>SHANDONG HI-SPEED GROUP</t>
+          <t>PDD HOLDINGS</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -7715,12 +7715,12 @@
       <c r="I125" s="9" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东高速集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“拼多多控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG HI-SPEED GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PDD HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L125" s="9" t="inlineStr">
@@ -7737,22 +7737,22 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>r414_guangdongguangxinholdingsgroup</t>
+          <t>r447_nucor</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>447</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>广东省广新控股集团有限公司</t>
+          <t>纽柯</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>GUANGDONG GUANGXIN HOLDINGS GROUP</t>
+          <t>NUCOR</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -7770,12 +7770,12 @@
       <c r="I126" s="9" t="inlineStr"/>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广东省广新控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“纽柯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGDONG GUANGXIN HOLDINGS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'NUCOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L126" s="9" t="inlineStr">
@@ -7792,22 +7792,22 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>r417_guangzhoupharmaceuticalholdings</t>
+          <t>r452_shanghaidelongsteelgroup</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>452</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>广州医药集团有限公司</t>
+          <t>上海德龙钢铁集团有限公司</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>GUANGZHOU PHARMACEUTICAL HOLDINGS</t>
+          <t>SHANGHAI DELONG STEEL GROUP</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -7825,12 +7825,12 @@
       <c r="I127" s="9" t="inlineStr"/>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广州医药集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“上海德龙钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGZHOU PHARMACEUTICAL HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI DELONG STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L127" s="9" t="inlineStr">
@@ -7847,22 +7847,22 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>r419_mapfregroup</t>
+          <t>r458_beijingjianlongheavyindustrygroup</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>458</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>曼福集团</t>
+          <t>北京建龙重工集团有限公司</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>MAPFRE GROUP</t>
+          <t>BEIJING JIANLONG HEAVY INDUSTRY GROUP</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
@@ -7880,12 +7880,12 @@
       <c r="I128" s="9" t="inlineStr"/>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“曼福集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“北京建龙重工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'MAPFRE GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BEIJING JIANLONG HEAVY INDUSTRY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L128" s="9" t="inlineStr">
@@ -7902,22 +7902,22 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>r420_cfe公司</t>
+          <t>r460_shaanxiconstructionengineeringholding</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>460</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>CFE公司</t>
+          <t>陕西建工控股集团有限公司</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>CFE公司</t>
+          <t>SHAANXI CONSTRUCTION ENGINEERING HOLDING</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -7935,12 +7935,12 @@
       <c r="I129" s="9" t="inlineStr"/>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“CFE公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“陕西建工控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CFE公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI CONSTRUCTION ENGINEERING HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L129" s="9" t="inlineStr">
@@ -7957,22 +7957,22 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>r043_chinarailwayconstruction</t>
+          <t>r465_cpc</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>465</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>中国铁道建筑集团有限公司</t>
+          <t>台湾中油股份有限公司</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>CHINA RAILWAY CONSTRUCTION</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="I130" s="9" t="inlineStr"/>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国铁道建筑集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“台湾中油股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA RAILWAY CONSTRUCTION'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CPC'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L130" s="9" t="inlineStr">
@@ -8012,22 +8012,22 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>r430_usfoodsholding公司</t>
+          <t>r471_shanxicokingcoalgroup</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>471</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>US Foods Holding公司</t>
+          <t>山西焦煤集团有限责任公司</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>US Foods Holding公司</t>
+          <t>SHANXI COKING COAL GROUP</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -8045,12 +8045,12 @@
       <c r="I131" s="9" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“US Foods Holding公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山西焦煤集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'US Foods Holding公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANXI COKING COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L131" s="9" t="inlineStr">
@@ -8067,22 +8067,22 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>r432_migros集团</t>
+          <t>r472_guangxiinvestmentgroup</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>472</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Migros集团</t>
+          <t>广西投资集团有限公司</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Migros集团</t>
+          <t>GUANGXI INVESTMENT GROUP</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -8100,12 +8100,12 @@
       <c r="I132" s="9" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Migros集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“广西投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Migros集团'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGXI INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L132" s="9" t="inlineStr">
@@ -8122,22 +8122,22 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>r435_chinaelectronics</t>
+          <t>r476_powercorpofcanada</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>476</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>中国电子信息产业集团有限公司</t>
+          <t>加拿大鲍尔集团</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>CHINA ELECTRONICS</t>
+          <t>POWER CORP. OF CANADA</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -8155,12 +8155,12 @@
       <c r="I133" s="9" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国电子信息产业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大鲍尔集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA ELECTRONICS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'POWER CORP. OF CANADA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L133" s="9" t="inlineStr">
@@ -8177,22 +8177,22 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>r436_shudaoinvestmentgroup</t>
+          <t>r483_chinanationalaviationfuelgroup</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>483</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>中国航空油料集团有限公司</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>SHUDAO INVESTMENT GROUP</t>
+          <t>CHINA NATIONAL AVIATION FUEL GROUP</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -8210,12 +8210,12 @@
       <c r="I134" s="9" t="inlineStr"/>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“蜀道投资集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国航空油料集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHUDAO INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL AVIATION FUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L134" s="9" t="inlineStr">
@@ -8232,22 +8232,22 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>r437_chinanationalcoalgroup</t>
+          <t>r488_luxshareprecisionindustry</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>488</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>中国中煤能源集团有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL COAL GROUP</t>
+          <t>LUXSHARE PRECISION INDUSTRY</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -8265,12 +8265,12 @@
       <c r="I135" s="9" t="inlineStr"/>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国中煤能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“立讯精密工业股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'LUXSHARE PRECISION INDUSTRY'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L135" s="9" t="inlineStr">
@@ -8287,22 +8287,22 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>r438_tonglingnonferrousmetalsgroup</t>
+          <t>r490_visa公司</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>490</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>铜陵有色金属集团控股有限公司</t>
+          <t>Visa公司</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>TONGLING NONFERROUS METALS GROUP</t>
+          <t>Visa公司</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
@@ -8320,12 +8320,12 @@
       <c r="I136" s="9" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“铜陵有色金属集团控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Visa公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'TONGLING NONFERROUS METALS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Visa公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L136" s="9" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>r439_ckhutchisonholdings</t>
+          <t>r496_airfranceklmgroup</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>496</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>长江和记实业有限公司</t>
+          <t>法国航空－荷兰皇家航空集团</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>CK HUTCHISON HOLDINGS</t>
+          <t>AIR FRANCE-KLM GROUP</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -8375,12 +8375,12 @@
       <c r="I137" s="9" t="inlineStr"/>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“长江和记实业有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国航空－荷兰皇家航空集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CK HUTCHISON HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'AIR FRANCE-KLM GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L137" s="9" t="inlineStr">
@@ -8397,22 +8397,22 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>r442_pddholdings</t>
+          <t>r497_enbridge公司</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>497</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>拼多多控股公司</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>PDD HOLDINGS</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -8430,12 +8430,12 @@
       <c r="I138" s="9" t="inlineStr"/>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“拼多多控股公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PDD HOLDINGS'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L138" s="9" t="inlineStr">
@@ -8452,22 +8452,22 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>r447_nucor</t>
+          <t>r499_enbridge公司</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>499</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>纽柯</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>NUCOR</t>
+          <t>Enbridge公司</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -8485,12 +8485,12 @@
       <c r="I139" s="9" t="inlineStr"/>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“纽柯”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'NUCOR'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L139" s="9" t="inlineStr">
@@ -8507,22 +8507,22 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>r452_shanghaidelongsteelgroup</t>
+          <t>r051_kroger</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>上海德龙钢铁集团有限公司</t>
+          <t>克罗格</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>SHANGHAI DELONG STEEL GROUP</t>
+          <t>KROGER</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -8540,12 +8540,12 @@
       <c r="I140" s="9" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“上海德龙钢铁集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“克罗格”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANGHAI DELONG STEEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'KROGER'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L140" s="9" t="inlineStr">
@@ -8562,22 +8562,22 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>r458_beijingjianlongheavyindustrygroup</t>
+          <t>r064_bnpparibas</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>北京建龙重工集团有限公司</t>
+          <t>法国巴黎银行</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>BEIJING JIANLONG HEAVY INDUSTRY GROUP</t>
+          <t>BNP PARIBAS</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -8595,12 +8595,12 @@
       <c r="I141" s="9" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“北京建龙重工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“法国巴黎银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BEIJING JIANLONG HEAVY INDUSTRY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BNP PARIBAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L141" s="9" t="inlineStr">
@@ -8617,22 +8617,22 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>r460_shaanxiconstructionengineeringholding</t>
+          <t>r075_shandongenergygroup</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>陕西建工控股集团有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>SHAANXI CONSTRUCTION ENGINEERING HOLDING</t>
+          <t>SHANDONG ENERGY GROUP</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -8650,12 +8650,12 @@
       <c r="I142" s="9" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“陕西建工控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHAANXI CONSTRUCTION ENGINEERING HOLDING'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG ENERGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L142" s="9" t="inlineStr">
@@ -8672,22 +8672,22 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>r465_cpc</t>
+          <t>r076_comcast</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>台湾中油股份有限公司</t>
+          <t>美国康卡斯特电信公司</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>COMCAST</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -8705,12 +8705,12 @@
       <c r="I143" s="9" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“台湾中油股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国康卡斯特电信公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CPC'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'COMCAST'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L143" s="9" t="inlineStr">
@@ -8727,22 +8727,22 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>r471_shanxicokingcoalgroup</t>
+          <t>r080_wellsfargo</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>山西焦煤集团有限责任公司</t>
+          <t>美国富国银行</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>SHANXI COKING COAL GROUP</t>
+          <t>WELLS FARGO</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -8760,12 +8760,12 @@
       <c r="I144" s="9" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山西焦煤集团有限责任公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国富国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANXI COKING COAL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'WELLS FARGO'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L144" s="9" t="inlineStr">
@@ -8782,22 +8782,22 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>r472_guangxiinvestmentgroup</t>
+          <t>r081_hengligroup</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司</t>
+          <t>恒力集团有限公司</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>GUANGXI INVESTMENT GROUP</t>
+          <t>HENGLI GROUP</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -8815,12 +8815,12 @@
       <c r="I145" s="9" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“广西投资集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GUANGXI INVESTMENT GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HENGLI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr">
@@ -8837,22 +8837,22 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>r476_powercorpofcanada</t>
+          <t>r083_chinapostgroup</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>加拿大鲍尔集团</t>
+          <t>中国邮政集团有限公司</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>POWER CORP. OF CANADA</t>
+          <t>CHINA POST GROUP</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -8870,12 +8870,12 @@
       <c r="I146" s="9" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“加拿大鲍尔集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'POWER CORP. OF CANADA'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA POST GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L146" s="9" t="inlineStr">
@@ -8892,22 +8892,22 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>r483_chinanationalaviationfuelgroup</t>
+          <t>r088_freddiemac</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>中国航空油料集团有限公司</t>
+          <t>房地美</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL AVIATION FUEL GROUP</t>
+          <t>FREDDIE MAC</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -8925,12 +8925,12 @@
       <c r="I147" s="9" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国航空油料集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“房地美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL AVIATION FUEL GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'FREDDIE MAC'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr">
@@ -8947,22 +8947,22 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>r488_luxshareprecisionindustry</t>
+          <t>r009_berkshirehathaway</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>伯克希尔－哈撒韦公司</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>LUXSHARE PRECISION INDUSTRY</t>
+          <t>BERKSHIRE HATHAWAY</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
@@ -8980,12 +8980,12 @@
       <c r="I148" s="9" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“立讯精密工业股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“伯克希尔－哈撒韦公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LUXSHARE PRECISION INDUSTRY'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'BERKSHIRE HATHAWAY'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L148" s="9" t="inlineStr">
@@ -9002,22 +9002,22 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>r490_visa公司</t>
+          <t>r092_humana</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Visa公司</t>
+          <t>哈门那公司</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Visa公司</t>
+          <t>HUMANA</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
@@ -9035,12 +9035,12 @@
       <c r="I149" s="9" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Visa公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“哈门那公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Visa公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'HUMANA'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L149" s="9" t="inlineStr">
@@ -9057,22 +9057,22 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>r496_airfranceklmgroup</t>
+          <t>r099_petrobras</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>法国航空－荷兰皇家航空集团</t>
+          <t>巴西国家石油公司</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>AIR FRANCE-KLM GROUP</t>
+          <t>PETROBRAS</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -9090,12 +9090,12 @@
       <c r="I150" s="9" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国航空－荷兰皇家航空集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“巴西国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'AIR FRANCE-KLM GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
+          <t>No file in the current corpus can be safely attributed to the parent company 'PETROBRAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr">
@@ -9109,1108 +9109,8 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>r497_enbridge公司</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>Enbridge公司</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>Enbridge公司</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G151" s="4" t="inlineStr"/>
-      <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="9" t="inlineStr"/>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K151" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M151" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>r499_enbridge公司</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>Enbridge公司</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>Enbridge公司</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr"/>
-      <c r="H152" s="4" t="inlineStr"/>
-      <c r="I152" s="9" t="inlineStr"/>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Enbridge公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'Enbridge公司'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L152" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M152" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>r005_sinopecgroup</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>中国石油化工集团有限公司</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>SINOPEC GROUP</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr"/>
-      <c r="H153" s="4" t="inlineStr"/>
-      <c r="I153" s="9" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油化工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SINOPEC GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L153" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M153" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>r051_kroger</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>克罗格</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>KROGER</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G154" s="4" t="inlineStr"/>
-      <c r="H154" s="4" t="inlineStr"/>
-      <c r="I154" s="9" t="inlineStr"/>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“克罗格”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K154" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'KROGER'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L154" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M154" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>r058_fanniemae</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>房利美</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>FANNIE MAE</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr"/>
-      <c r="H155" s="4" t="inlineStr"/>
-      <c r="I155" s="9" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“房利美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FANNIE MAE'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L155" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M155" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="9" t="inlineStr">
-        <is>
-          <t>r059_chinalifeinsurance</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>中国人寿保险（集团）公司</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="inlineStr">
-        <is>
-          <t>CHINA LIFE INSURANCE</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr"/>
-      <c r="H156" s="4" t="inlineStr"/>
-      <c r="I156" s="9" t="inlineStr"/>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国人寿保险（集团）公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA LIFE INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L156" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M156" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>r006_chinanationalpetroleum</t>
-        </is>
-      </c>
-      <c r="B157" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
-        <is>
-          <t>中国石油天然气集团有限公司</t>
-        </is>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>CHINA NATIONAL PETROLEUM</t>
-        </is>
-      </c>
-      <c r="E157" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr"/>
-      <c r="H157" s="4" t="inlineStr"/>
-      <c r="I157" s="9" t="inlineStr"/>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油天然气集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA NATIONAL PETROLEUM'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L157" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M157" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>r064_bnpparibas</t>
-        </is>
-      </c>
-      <c r="B158" s="9" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
-        <is>
-          <t>法国巴黎银行</t>
-        </is>
-      </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>BNP PARIBAS</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr"/>
-      <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="9" t="inlineStr"/>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“法国巴黎银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BNP PARIBAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L158" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M158" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>r075_shandongenergygroup</t>
-        </is>
-      </c>
-      <c r="B159" s="9" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="inlineStr">
-        <is>
-          <t>山东能源集团有限公司</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>SHANDONG ENERGY GROUP</t>
-        </is>
-      </c>
-      <c r="E159" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F159" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr"/>
-      <c r="H159" s="4" t="inlineStr"/>
-      <c r="I159" s="9" t="inlineStr"/>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K159" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'SHANDONG ENERGY GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L159" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M159" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>r076_comcast</t>
-        </is>
-      </c>
-      <c r="B160" s="9" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>美国康卡斯特电信公司</t>
-        </is>
-      </c>
-      <c r="D160" s="9" t="inlineStr">
-        <is>
-          <t>COMCAST</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr"/>
-      <c r="H160" s="4" t="inlineStr"/>
-      <c r="I160" s="9" t="inlineStr"/>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国康卡斯特电信公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'COMCAST'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L160" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M160" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="inlineStr">
-        <is>
-          <t>r080_wellsfargo</t>
-        </is>
-      </c>
-      <c r="B161" s="9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="inlineStr">
-        <is>
-          <t>美国富国银行</t>
-        </is>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>WELLS FARGO</t>
-        </is>
-      </c>
-      <c r="E161" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr"/>
-      <c r="H161" s="4" t="inlineStr"/>
-      <c r="I161" s="9" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国富国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'WELLS FARGO'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L161" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M161" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>r081_hengligroup</t>
-        </is>
-      </c>
-      <c r="B162" s="9" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr">
-        <is>
-          <t>恒力集团有限公司</t>
-        </is>
-      </c>
-      <c r="D162" s="9" t="inlineStr">
-        <is>
-          <t>HENGLI GROUP</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="inlineStr"/>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="9" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HENGLI GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L162" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M162" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>r083_chinapostgroup</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>中国邮政集团有限公司</t>
-        </is>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>CHINA POST GROUP</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr"/>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="9" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'CHINA POST GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L163" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M163" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="9" t="inlineStr">
-        <is>
-          <t>r087_goldmansachsgroup</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>高盛集团</t>
-        </is>
-      </c>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>GOLDMAN SACHS GROUP</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="inlineStr"/>
-      <c r="H164" s="4" t="inlineStr"/>
-      <c r="I164" s="9" t="inlineStr"/>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“高盛集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'GOLDMAN SACHS GROUP'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L164" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M164" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="9" t="inlineStr">
-        <is>
-          <t>r088_freddiemac</t>
-        </is>
-      </c>
-      <c r="B165" s="9" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>房地美</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>FREDDIE MAC</t>
-        </is>
-      </c>
-      <c r="E165" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr"/>
-      <c r="H165" s="4" t="inlineStr"/>
-      <c r="I165" s="9" t="inlineStr"/>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“房地美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'FREDDIE MAC'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L165" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M165" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="9" t="inlineStr">
-        <is>
-          <t>r009_berkshirehathaway</t>
-        </is>
-      </c>
-      <c r="B166" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>伯克希尔－哈撒韦公司</t>
-        </is>
-      </c>
-      <c r="D166" s="9" t="inlineStr">
-        <is>
-          <t>BERKSHIRE HATHAWAY</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr"/>
-      <c r="H166" s="4" t="inlineStr"/>
-      <c r="I166" s="9" t="inlineStr"/>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“伯克希尔－哈撒韦公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'BERKSHIRE HATHAWAY'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L166" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M166" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>r092_humana</t>
-        </is>
-      </c>
-      <c r="B167" s="9" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>哈门那公司</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>HUMANA</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr"/>
-      <c r="H167" s="4" t="inlineStr"/>
-      <c r="I167" s="9" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“哈门那公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'HUMANA'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L167" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M167" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t>r094_statefarminsurance</t>
-        </is>
-      </c>
-      <c r="B168" s="9" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="inlineStr">
-        <is>
-          <t>州立农业保险公司</t>
-        </is>
-      </c>
-      <c r="D168" s="9" t="inlineStr">
-        <is>
-          <t>STATE FARM INSURANCE</t>
-        </is>
-      </c>
-      <c r="E168" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr"/>
-      <c r="H168" s="4" t="inlineStr"/>
-      <c r="I168" s="9" t="inlineStr"/>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“州立农业保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K168" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'STATE FARM INSURANCE'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L168" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M168" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>r095_lifeinsurancecorpofindia</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>印度人寿保险公司</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
-        <is>
-          <t>LIFE INSURANCE CORP. OF INDIA</t>
-        </is>
-      </c>
-      <c r="E169" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G169" s="4" t="inlineStr"/>
-      <c r="H169" s="4" t="inlineStr"/>
-      <c r="I169" s="9" t="inlineStr"/>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度人寿保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'LIFE INSURANCE CORP. OF INDIA'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L169" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M169" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="9" t="inlineStr">
-        <is>
-          <t>r099_petrobras</t>
-        </is>
-      </c>
-      <c r="B170" s="9" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>巴西国家石油公司</t>
-        </is>
-      </c>
-      <c r="D170" s="9" t="inlineStr">
-        <is>
-          <t>PETROBRAS</t>
-        </is>
-      </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>库内无母公司主报告</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>No parent-company main report in corpus</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr"/>
-      <c r="H170" s="4" t="inlineStr"/>
-      <c r="I170" s="9" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>在当前库存文件中，未检出能够安全归属于“巴西国家石油公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
-        </is>
-      </c>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>No file in the current corpus can be safely attributed to the parent company 'PETROBRAS'. Available file-name evidence is insufficient for a reliable manual match.</t>
-        </is>
-      </c>
-      <c r="L170" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M170" s="9" t="inlineStr">
-        <is>
-          <t>default_no_parent_report</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:M170"/>
+  <autoFilter ref="A3:M150"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
